--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_environmental_waste_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>6.57142857142857</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>70.06688036049709</v>
       </c>
       <c r="G2">
         <v>4.02906976744186</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.189709302325581</v>
       </c>
       <c r="I2">
         <v>0.212381244253754</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>25.7</v>
       </c>
       <c r="L2">
-        <v>34.0959830549019</v>
+        <v>33.742092112368</v>
       </c>
       <c r="M2">
         <v>23.86</v>
       </c>
       <c r="N2">
-        <v>25.3259830549019</v>
+        <v>25.298392112368</v>
       </c>
       <c r="O2">
         <v>6.93</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.3263</v>
       </c>
       <c r="Q2">
         <v>0.0895960325001434</v>
       </c>
       <c r="R2">
-        <v>0.0870609190011743</v>
+        <v>0.0871059190011743</v>
       </c>
       <c r="S2">
         <v>0.0577366166625341</v>
@@ -1191,13 +1191,13 @@
         <v>0.0981869177824248</v>
       </c>
       <c r="X2">
-        <v>0.0870609190011743</v>
+        <v>0.0874776959607821</v>
       </c>
       <c r="Y2">
         <v>1.02111853529825</v>
       </c>
       <c r="Z2">
-        <v>0.804252110241037</v>
+        <v>0.812375868930341</v>
       </c>
       <c r="AA2">
         <v>6.93</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08706091900117428</v>
+        <v>0.0871059190011743</v>
       </c>
       <c r="C2">
-        <v>34.09598305490192</v>
+        <v>33.74209211236802</v>
       </c>
       <c r="D2">
-        <v>25.32598305490192</v>
+        <v>25.29839211236802</v>
       </c>
       <c r="E2">
-        <v>-6.93</v>
+        <v>-6.6037</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3263</v>
       </c>
       <c r="G2">
         <v>8.77</v>
@@ -1451,28 +1451,28 @@
         <v>1.15</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01641289</v>
       </c>
       <c r="N2">
-        <v>1.15</v>
+        <v>1.13358711</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.15</v>
+        <v>1.13358711</v>
       </c>
       <c r="Q2">
-        <v>1.72</v>
+        <v>1.70358711</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08706091900117428</v>
+        <v>0.08747769596078211</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8123758689303407</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>70.06688036049714</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0871059190011743</v>
+        <v>0.08715091900117428</v>
       </c>
       <c r="C3">
-        <v>33.74209211236802</v>
+        <v>33.38826122133695</v>
       </c>
       <c r="D3">
-        <v>25.29839211236802</v>
+        <v>25.27086122133695</v>
       </c>
       <c r="E3">
-        <v>-6.6037</v>
+        <v>-6.2774</v>
       </c>
       <c r="F3">
-        <v>0.3263</v>
+        <v>0.6526</v>
       </c>
       <c r="G3">
         <v>8.77</v>
@@ -1533,28 +1533,28 @@
         <v>1.15</v>
       </c>
       <c r="M3">
-        <v>0.01641289</v>
+        <v>0.03282578</v>
       </c>
       <c r="N3">
-        <v>1.13358711</v>
+        <v>1.11717422</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.13358711</v>
+        <v>1.11717422</v>
       </c>
       <c r="Q3">
-        <v>1.70358711</v>
+        <v>1.68717422</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08747769596078211</v>
+        <v>0.08790297857262683</v>
       </c>
       <c r="T3">
-        <v>0.8123758689303407</v>
+        <v>0.8206654186133033</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>70.06688036049714</v>
+        <v>35.03344018024857</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08715091900117428</v>
+        <v>0.08719591900117428</v>
       </c>
       <c r="C4">
-        <v>33.38826122133695</v>
+        <v>33.03449018596924</v>
       </c>
       <c r="D4">
-        <v>25.27086122133695</v>
+        <v>25.24339018596924</v>
       </c>
       <c r="E4">
-        <v>-6.2774</v>
+        <v>-5.9511</v>
       </c>
       <c r="F4">
-        <v>0.6526</v>
+        <v>0.9788999999999999</v>
       </c>
       <c r="G4">
         <v>8.77</v>
@@ -1615,28 +1615,28 @@
         <v>1.15</v>
       </c>
       <c r="M4">
-        <v>0.03282578</v>
+        <v>0.04923866999999999</v>
       </c>
       <c r="N4">
-        <v>1.11717422</v>
+        <v>1.10076133</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.11717422</v>
+        <v>1.10076133</v>
       </c>
       <c r="Q4">
-        <v>1.68717422</v>
+        <v>1.67076133</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08790297857262683</v>
+        <v>0.08833702989811781</v>
       </c>
       <c r="T4">
-        <v>0.8206654186133033</v>
+        <v>0.8291258868464301</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.03344018024857</v>
+        <v>23.35562678683239</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08719591900117428</v>
+        <v>0.08724091900117428</v>
       </c>
       <c r="C5">
-        <v>33.03449018596924</v>
+        <v>32.68077881127611</v>
       </c>
       <c r="D5">
-        <v>25.24339018596924</v>
+        <v>25.21597881127612</v>
       </c>
       <c r="E5">
-        <v>-5.9511</v>
+        <v>-5.6248</v>
       </c>
       <c r="F5">
-        <v>0.9788999999999999</v>
+        <v>1.3052</v>
       </c>
       <c r="G5">
         <v>8.77</v>
@@ -1697,28 +1697,28 @@
         <v>1.15</v>
       </c>
       <c r="M5">
-        <v>0.04923866999999999</v>
+        <v>0.06565156</v>
       </c>
       <c r="N5">
-        <v>1.10076133</v>
+        <v>1.08434844</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.10076133</v>
+        <v>1.08434844</v>
       </c>
       <c r="Q5">
-        <v>1.67076133</v>
+        <v>1.65434844</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08833702989811781</v>
+        <v>0.08878012395955655</v>
       </c>
       <c r="T5">
-        <v>0.8291258868464301</v>
+        <v>0.8377626148344138</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.35562678683239</v>
+        <v>17.51672009012428</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08724091900117428</v>
+        <v>0.08728591900117429</v>
       </c>
       <c r="C6">
-        <v>32.68077881127611</v>
+        <v>32.3271269031148</v>
       </c>
       <c r="D6">
-        <v>25.21597881127612</v>
+        <v>25.18862690311481</v>
       </c>
       <c r="E6">
-        <v>-5.6248</v>
+        <v>-5.2985</v>
       </c>
       <c r="F6">
-        <v>1.3052</v>
+        <v>1.6315</v>
       </c>
       <c r="G6">
         <v>8.77</v>
@@ -1779,28 +1779,28 @@
         <v>1.15</v>
       </c>
       <c r="M6">
-        <v>0.06565156</v>
+        <v>0.08206445</v>
       </c>
       <c r="N6">
-        <v>1.08434844</v>
+        <v>1.06793555</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.08434844</v>
+        <v>1.06793555</v>
       </c>
       <c r="Q6">
-        <v>1.65434844</v>
+        <v>1.63793555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08878012395955655</v>
+        <v>0.08923254631702557</v>
       </c>
       <c r="T6">
-        <v>0.8377626148344138</v>
+        <v>0.8465811686747761</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.51672009012428</v>
+        <v>14.01337607209943</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08728591900117429</v>
+        <v>0.08742091900117428</v>
       </c>
       <c r="C7">
-        <v>32.3271269031148</v>
+        <v>31.91912604898844</v>
       </c>
       <c r="D7">
-        <v>25.18862690311481</v>
+        <v>25.10692604898844</v>
       </c>
       <c r="E7">
-        <v>-5.2985</v>
+        <v>-4.9722</v>
       </c>
       <c r="F7">
-        <v>1.6315</v>
+        <v>1.9578</v>
       </c>
       <c r="G7">
         <v>8.77</v>
@@ -1861,45 +1861,45 @@
         <v>1.15</v>
       </c>
       <c r="M7">
-        <v>0.08206445</v>
+        <v>0.10141404</v>
       </c>
       <c r="N7">
-        <v>1.06793555</v>
+        <v>1.04858596</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.06793555</v>
+        <v>1.04858596</v>
       </c>
       <c r="Q7">
-        <v>1.63793555</v>
+        <v>1.61858596</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08923254631702557</v>
+        <v>0.08969459468210031</v>
       </c>
       <c r="T7">
-        <v>0.8465811686747761</v>
+        <v>0.8555873513202524</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.01337607209943</v>
+        <v>11.33965277391572</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08742091900117428</v>
+        <v>0.0875999190011743</v>
       </c>
       <c r="C8">
-        <v>31.91912604898844</v>
+        <v>31.48531053531859</v>
       </c>
       <c r="D8">
-        <v>25.10692604898844</v>
+        <v>24.99941053531859</v>
       </c>
       <c r="E8">
-        <v>-4.9722</v>
+        <v>-4.6459</v>
       </c>
       <c r="F8">
-        <v>1.9578</v>
+        <v>2.2841</v>
       </c>
       <c r="G8">
         <v>8.77</v>
@@ -1943,45 +1943,45 @@
         <v>1.15</v>
       </c>
       <c r="M8">
-        <v>0.10141404</v>
+        <v>0.12219935</v>
       </c>
       <c r="N8">
-        <v>1.04858596</v>
+        <v>1.02780065</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.04858596</v>
+        <v>1.02780065</v>
       </c>
       <c r="Q8">
-        <v>1.61858596</v>
+        <v>1.59780065</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08969459468210031</v>
+        <v>0.09016657957115515</v>
       </c>
       <c r="T8">
-        <v>0.8555873513202524</v>
+        <v>0.8647872153129432</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.33965277391572</v>
+        <v>9.410852021716973</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08759991900117428</v>
+        <v>0.08767691900117429</v>
       </c>
       <c r="C9">
-        <v>31.4853105353186</v>
+        <v>31.11304357649898</v>
       </c>
       <c r="D9">
-        <v>24.9994105353186</v>
+        <v>24.95344357649898</v>
       </c>
       <c r="E9">
-        <v>-4.645899999999999</v>
+        <v>-4.319599999999999</v>
       </c>
       <c r="F9">
-        <v>2.2841</v>
+        <v>2.6104</v>
       </c>
       <c r="G9">
         <v>8.77</v>
@@ -2025,28 +2025,28 @@
         <v>1.15</v>
       </c>
       <c r="M9">
-        <v>0.12219935</v>
+        <v>0.1396564</v>
       </c>
       <c r="N9">
-        <v>1.02780065</v>
+        <v>1.0103436</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.02780065</v>
+        <v>1.0103436</v>
       </c>
       <c r="Q9">
-        <v>1.59780065</v>
+        <v>1.5803436</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09016657957115515</v>
+        <v>0.09064882500127638</v>
       </c>
       <c r="T9">
-        <v>0.8647872153129432</v>
+        <v>0.8741870763489535</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.410852021716972</v>
+        <v>8.234495519002351</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08767691900117429</v>
+        <v>0.0878259190011743</v>
       </c>
       <c r="C10">
-        <v>31.11304357649898</v>
+        <v>30.69827286172901</v>
       </c>
       <c r="D10">
-        <v>24.95344357649898</v>
+        <v>24.86497286172901</v>
       </c>
       <c r="E10">
-        <v>-4.319599999999999</v>
+        <v>-3.9933</v>
       </c>
       <c r="F10">
-        <v>2.6104</v>
+        <v>2.9367</v>
       </c>
       <c r="G10">
         <v>8.77</v>
@@ -2107,45 +2107,45 @@
         <v>1.15</v>
       </c>
       <c r="M10">
-        <v>0.1396564</v>
+        <v>0.15946281</v>
       </c>
       <c r="N10">
-        <v>1.0103436</v>
+        <v>0.99053719</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.0103436</v>
+        <v>0.99053719</v>
       </c>
       <c r="Q10">
-        <v>1.5803436</v>
+        <v>1.56053719</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09064882500127638</v>
+        <v>0.09114166923205966</v>
       </c>
       <c r="T10">
-        <v>0.8741870763489535</v>
+        <v>0.8837935277374037</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.234495519002351</v>
+        <v>7.211712875246586</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0878259190011743</v>
+        <v>0.08791091900117429</v>
       </c>
       <c r="C11">
-        <v>30.69827286172901</v>
+        <v>30.32178343952268</v>
       </c>
       <c r="D11">
-        <v>24.86497286172901</v>
+        <v>24.81478343952267</v>
       </c>
       <c r="E11">
-        <v>-3.9933</v>
+        <v>-3.667</v>
       </c>
       <c r="F11">
-        <v>2.9367</v>
+        <v>3.262999999999999</v>
       </c>
       <c r="G11">
         <v>8.77</v>
@@ -2189,28 +2189,28 @@
         <v>1.15</v>
       </c>
       <c r="M11">
-        <v>0.15946281</v>
+        <v>0.1771809</v>
       </c>
       <c r="N11">
-        <v>0.99053719</v>
+        <v>0.9728190999999999</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0.99053719</v>
+        <v>0.9728190999999999</v>
       </c>
       <c r="Q11">
-        <v>1.56053719</v>
+        <v>1.5428191</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09114166923205966</v>
+        <v>0.09164546555686032</v>
       </c>
       <c r="T11">
-        <v>0.8837935277374037</v>
+        <v>0.8936134558233748</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.211712875246586</v>
+        <v>6.490541587721927</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08791091900117429</v>
+        <v>0.0881059190011743</v>
       </c>
       <c r="C12">
-        <v>30.32178343952268</v>
+        <v>29.88110505264558</v>
       </c>
       <c r="D12">
-        <v>24.81478343952267</v>
+        <v>24.70040505264558</v>
       </c>
       <c r="E12">
-        <v>-3.667</v>
+        <v>-3.3407</v>
       </c>
       <c r="F12">
-        <v>3.263</v>
+        <v>3.5893</v>
       </c>
       <c r="G12">
         <v>8.77</v>
@@ -2271,45 +2271,45 @@
         <v>1.15</v>
       </c>
       <c r="M12">
-        <v>0.1771809</v>
+        <v>0.19848829</v>
       </c>
       <c r="N12">
-        <v>0.9728190999999999</v>
+        <v>0.9515117099999999</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0.9728190999999999</v>
+        <v>0.9515117099999999</v>
       </c>
       <c r="Q12">
-        <v>1.5428191</v>
+        <v>1.52151171</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09164546555686032</v>
+        <v>0.09216058314738684</v>
       </c>
       <c r="T12">
-        <v>0.8936134558233748</v>
+        <v>0.9036540564506037</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.490541587721927</v>
+        <v>5.793792671597906</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0881059190011743</v>
+        <v>0.08820091900117429</v>
       </c>
       <c r="C13">
-        <v>29.88110505264558</v>
+        <v>29.49946336347286</v>
       </c>
       <c r="D13">
-        <v>24.70040505264558</v>
+        <v>24.64506336347286</v>
       </c>
       <c r="E13">
-        <v>-3.3407</v>
+        <v>-3.0144</v>
       </c>
       <c r="F13">
-        <v>3.5893</v>
+        <v>3.9156</v>
       </c>
       <c r="G13">
         <v>8.77</v>
@@ -2353,28 +2353,28 @@
         <v>1.15</v>
       </c>
       <c r="M13">
-        <v>0.19848829</v>
+        <v>0.21653268</v>
       </c>
       <c r="N13">
-        <v>0.9515117099999999</v>
+        <v>0.9334673199999999</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.9515117099999999</v>
+        <v>0.9334673199999999</v>
       </c>
       <c r="Q13">
-        <v>1.52151171</v>
+        <v>1.50346732</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09216058314738684</v>
+        <v>0.09268740795587986</v>
       </c>
       <c r="T13">
-        <v>0.9036540564506037</v>
+        <v>0.9139228525466332</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.793792671597906</v>
+        <v>5.310976615631414</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08820091900117429</v>
+        <v>0.08829591900117427</v>
       </c>
       <c r="C14">
-        <v>29.49946336347286</v>
+        <v>29.11806910796411</v>
       </c>
       <c r="D14">
-        <v>24.64506336347286</v>
+        <v>24.58996910796411</v>
       </c>
       <c r="E14">
-        <v>-3.0144</v>
+        <v>-2.6881</v>
       </c>
       <c r="F14">
-        <v>3.9156</v>
+        <v>4.241899999999999</v>
       </c>
       <c r="G14">
         <v>8.77</v>
@@ -2435,28 +2435,28 @@
         <v>1.15</v>
       </c>
       <c r="M14">
-        <v>0.21653268</v>
+        <v>0.23457707</v>
       </c>
       <c r="N14">
-        <v>0.9334673199999999</v>
+        <v>0.91542293</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.9334673199999999</v>
+        <v>0.91542293</v>
       </c>
       <c r="Q14">
-        <v>1.50346732</v>
+        <v>1.48542293</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09268740795587986</v>
+        <v>0.09322634367951066</v>
       </c>
       <c r="T14">
-        <v>0.9139228525466332</v>
+        <v>0.9244277129207324</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.310976615631414</v>
+        <v>4.902439952890536</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08829591900117427</v>
+        <v>0.08839091900117428</v>
       </c>
       <c r="C15">
-        <v>29.11806910796411</v>
+        <v>28.73692063040033</v>
       </c>
       <c r="D15">
-        <v>24.58996910796411</v>
+        <v>24.53512063040033</v>
       </c>
       <c r="E15">
-        <v>-2.6881</v>
+        <v>-2.3618</v>
       </c>
       <c r="F15">
-        <v>4.241899999999999</v>
+        <v>4.5682</v>
       </c>
       <c r="G15">
         <v>8.77</v>
@@ -2517,28 +2517,28 @@
         <v>1.15</v>
       </c>
       <c r="M15">
-        <v>0.23457707</v>
+        <v>0.25262146</v>
       </c>
       <c r="N15">
-        <v>0.91542293</v>
+        <v>0.8973785399999998</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0.91542293</v>
+        <v>0.8973785399999998</v>
       </c>
       <c r="Q15">
-        <v>1.48542293</v>
+        <v>1.46737854</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09322634367951066</v>
+        <v>0.09377781279206313</v>
       </c>
       <c r="T15">
-        <v>0.9244277129207324</v>
+        <v>0.9351768723732992</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.902439952890536</v>
+        <v>4.552265670541211</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08839091900117428</v>
+        <v>0.08886091900117428</v>
       </c>
       <c r="C16">
-        <v>28.73692063040033</v>
+        <v>28.14282544711654</v>
       </c>
       <c r="D16">
-        <v>24.53512063040033</v>
+        <v>24.26732544711654</v>
       </c>
       <c r="E16">
-        <v>-2.3618</v>
+        <v>-2.0355</v>
       </c>
       <c r="F16">
-        <v>4.5682</v>
+        <v>4.8945</v>
       </c>
       <c r="G16">
         <v>8.77</v>
@@ -2599,45 +2599,45 @@
         <v>1.15</v>
       </c>
       <c r="M16">
-        <v>0.25262146</v>
+        <v>0.2829021</v>
       </c>
       <c r="N16">
-        <v>0.8973785399999998</v>
+        <v>0.8670978999999999</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.8973785399999998</v>
+        <v>0.8670978999999999</v>
       </c>
       <c r="Q16">
-        <v>1.46737854</v>
+        <v>1.4370979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09377781279206313</v>
+        <v>0.09434225764844034</v>
       </c>
       <c r="T16">
-        <v>0.9351768723732992</v>
+        <v>0.9461789532247498</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.552265670541211</v>
+        <v>4.065010475355255</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08886091900117428</v>
+        <v>0.08954091900117428</v>
       </c>
       <c r="C17">
-        <v>28.14282544711654</v>
+        <v>27.43926356783146</v>
       </c>
       <c r="D17">
-        <v>24.26732544711654</v>
+        <v>23.89006356783146</v>
       </c>
       <c r="E17">
-        <v>-2.035500000000001</v>
+        <v>-1.7092</v>
       </c>
       <c r="F17">
-        <v>4.894499999999999</v>
+        <v>5.2208</v>
       </c>
       <c r="G17">
         <v>8.77</v>
@@ -2681,45 +2681,45 @@
         <v>1.15</v>
       </c>
       <c r="M17">
-        <v>0.2829020999999999</v>
+        <v>0.32003504</v>
       </c>
       <c r="N17">
-        <v>0.8670979</v>
+        <v>0.8299649599999999</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0.8670979</v>
+        <v>0.8299649599999999</v>
       </c>
       <c r="Q17">
-        <v>1.4370979</v>
+        <v>1.39996496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09434225764844034</v>
+        <v>0.09492014166806462</v>
       </c>
       <c r="T17">
-        <v>0.9461789532247498</v>
+        <v>0.9574429883821872</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.065010475355257</v>
+        <v>3.593356527460243</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08954091900117428</v>
+        <v>0.09017191900117429</v>
       </c>
       <c r="C18">
-        <v>27.43926356783146</v>
+        <v>26.77323000546507</v>
       </c>
       <c r="D18">
-        <v>23.89006356783146</v>
+        <v>23.55033000546507</v>
       </c>
       <c r="E18">
-        <v>-1.7092</v>
+        <v>-1.3829</v>
       </c>
       <c r="F18">
-        <v>5.2208</v>
+        <v>5.547099999999999</v>
       </c>
       <c r="G18">
         <v>8.77</v>
@@ -2763,45 +2763,45 @@
         <v>1.15</v>
       </c>
       <c r="M18">
-        <v>0.32003504</v>
+        <v>0.35556911</v>
       </c>
       <c r="N18">
-        <v>0.8299649599999999</v>
+        <v>0.7944308899999999</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0.8299649599999999</v>
+        <v>0.7944308899999999</v>
       </c>
       <c r="Q18">
-        <v>1.39996496</v>
+        <v>1.36443089</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09492014166806462</v>
+        <v>0.09551195060382445</v>
       </c>
       <c r="T18">
-        <v>0.9574429883821872</v>
+        <v>0.968978446073539</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.593356527460243</v>
+        <v>3.234251704260811</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09017191900117429</v>
+        <v>0.09035491900117429</v>
       </c>
       <c r="C19">
-        <v>26.77323000546507</v>
+        <v>26.35020195640529</v>
       </c>
       <c r="D19">
-        <v>23.55033000546507</v>
+        <v>23.45360195640529</v>
       </c>
       <c r="E19">
-        <v>-1.3829</v>
+        <v>-1.0566</v>
       </c>
       <c r="F19">
-        <v>5.547099999999999</v>
+        <v>5.8734</v>
       </c>
       <c r="G19">
         <v>8.77</v>
@@ -2845,28 +2845,28 @@
         <v>1.15</v>
       </c>
       <c r="M19">
-        <v>0.35556911</v>
+        <v>0.37648494</v>
       </c>
       <c r="N19">
-        <v>0.7944308899999999</v>
+        <v>0.7735150599999998</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0.7944308899999999</v>
+        <v>0.7735150599999998</v>
       </c>
       <c r="Q19">
-        <v>1.36443089</v>
+        <v>1.34351506</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09551195060382445</v>
+        <v>0.09611819390387108</v>
       </c>
       <c r="T19">
-        <v>0.968978446073539</v>
+        <v>0.9807952563915089</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.234251704260811</v>
+        <v>3.054571054024099</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09035491900117429</v>
+        <v>0.09201991900117429</v>
       </c>
       <c r="C20">
-        <v>26.35020195640529</v>
+        <v>25.17902277657759</v>
       </c>
       <c r="D20">
-        <v>23.45360195640529</v>
+        <v>22.60872277657759</v>
       </c>
       <c r="E20">
-        <v>-1.0566</v>
+        <v>-0.7303000000000006</v>
       </c>
       <c r="F20">
-        <v>5.873399999999999</v>
+        <v>6.199699999999999</v>
       </c>
       <c r="G20">
         <v>8.77</v>
@@ -2927,45 +2927,45 @@
         <v>1.15</v>
       </c>
       <c r="M20">
-        <v>0.37648494</v>
+        <v>0.44575843</v>
       </c>
       <c r="N20">
-        <v>0.7735150599999999</v>
+        <v>0.70424157</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0.7735150599999999</v>
+        <v>0.70424157</v>
       </c>
       <c r="Q20">
-        <v>1.34351506</v>
+        <v>1.27424157</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09611819390387108</v>
+        <v>0.09673940617428924</v>
       </c>
       <c r="T20">
-        <v>0.9807952563915089</v>
+        <v>0.9929038398037496</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.0545710540241</v>
+        <v>2.579872690237176</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09201991900117429</v>
+        <v>0.0930609190011743</v>
       </c>
       <c r="C21">
-        <v>25.17902277657759</v>
+        <v>24.35472821981002</v>
       </c>
       <c r="D21">
-        <v>22.60872277657759</v>
+        <v>22.11072821981002</v>
       </c>
       <c r="E21">
-        <v>-0.7303000000000006</v>
+        <v>-0.4039999999999999</v>
       </c>
       <c r="F21">
-        <v>6.199699999999999</v>
+        <v>6.526</v>
       </c>
       <c r="G21">
         <v>8.77</v>
@@ -3009,45 +3009,45 @@
         <v>1.15</v>
       </c>
       <c r="M21">
-        <v>0.44575843</v>
+        <v>0.4946708</v>
       </c>
       <c r="N21">
-        <v>0.70424157</v>
+        <v>0.6553291999999999</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0.70424157</v>
+        <v>0.6553291999999999</v>
       </c>
       <c r="Q21">
-        <v>1.27424157</v>
+        <v>1.2253292</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09673940617428924</v>
+        <v>0.09737614875146786</v>
       </c>
       <c r="T21">
-        <v>0.9929038398037496</v>
+        <v>1.005315137801297</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.579872690237176</v>
+        <v>2.32477841829354</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0930609190011743</v>
+        <v>0.0933609190011743</v>
       </c>
       <c r="C22">
-        <v>24.35472821981002</v>
+        <v>23.88896038350141</v>
       </c>
       <c r="D22">
-        <v>22.11072821981002</v>
+        <v>21.97126038350141</v>
       </c>
       <c r="E22">
-        <v>-0.4039999999999999</v>
+        <v>-0.0777000000000001</v>
       </c>
       <c r="F22">
-        <v>6.526</v>
+        <v>6.8523</v>
       </c>
       <c r="G22">
         <v>8.77</v>
@@ -3091,28 +3091,28 @@
         <v>1.15</v>
       </c>
       <c r="M22">
-        <v>0.4946708</v>
+        <v>0.51940434</v>
       </c>
       <c r="N22">
-        <v>0.6553291999999999</v>
+        <v>0.6305956599999999</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0.6553291999999999</v>
+        <v>0.6305956599999999</v>
       </c>
       <c r="Q22">
-        <v>1.2253292</v>
+        <v>1.20059566</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09737614875146786</v>
+        <v>0.0980290113938915</v>
       </c>
       <c r="T22">
-        <v>1.005315137801297</v>
+        <v>1.018040645874731</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.32477841829354</v>
+        <v>2.214074684089085</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0933609190011743</v>
+        <v>0.09366091900117428</v>
       </c>
       <c r="C23">
-        <v>23.88896038350141</v>
+        <v>23.42494096121267</v>
       </c>
       <c r="D23">
-        <v>21.97126038350141</v>
+        <v>21.83354096121267</v>
       </c>
       <c r="E23">
-        <v>-0.07770000000000099</v>
+        <v>0.2485999999999997</v>
       </c>
       <c r="F23">
-        <v>6.852299999999999</v>
+        <v>7.178599999999999</v>
       </c>
       <c r="G23">
         <v>8.77</v>
@@ -3173,28 +3173,28 @@
         <v>1.15</v>
       </c>
       <c r="M23">
-        <v>0.5194043399999999</v>
+        <v>0.54413788</v>
       </c>
       <c r="N23">
-        <v>0.63059566</v>
+        <v>0.6058621199999999</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0.63059566</v>
+        <v>0.6058621199999999</v>
       </c>
       <c r="Q23">
-        <v>1.20059566</v>
+        <v>1.17586212</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0980290113938915</v>
+        <v>0.09869861410406959</v>
       </c>
       <c r="T23">
-        <v>1.018040645874731</v>
+        <v>1.031092449026971</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.214074684089086</v>
+        <v>2.1134349257214</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09366091900117428</v>
+        <v>0.09396091900117429</v>
       </c>
       <c r="C24">
-        <v>23.42494096121267</v>
+        <v>22.96263727971722</v>
       </c>
       <c r="D24">
-        <v>21.83354096121267</v>
+        <v>21.69753727971722</v>
       </c>
       <c r="E24">
-        <v>0.2485999999999997</v>
+        <v>0.5748999999999995</v>
       </c>
       <c r="F24">
-        <v>7.178599999999999</v>
+        <v>7.504899999999999</v>
       </c>
       <c r="G24">
         <v>8.77</v>
@@ -3255,28 +3255,28 @@
         <v>1.15</v>
       </c>
       <c r="M24">
-        <v>0.54413788</v>
+        <v>0.56887142</v>
       </c>
       <c r="N24">
-        <v>0.6058621199999999</v>
+        <v>0.5811285799999999</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0.6058621199999999</v>
+        <v>0.5811285799999999</v>
       </c>
       <c r="Q24">
-        <v>1.17586212</v>
+        <v>1.15112858</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09869861410406959</v>
+        <v>0.09938560909243413</v>
       </c>
       <c r="T24">
-        <v>1.031092449026971</v>
+        <v>1.044483260053295</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.1134349257214</v>
+        <v>2.021546450690034</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09396091900117429</v>
+        <v>0.09766891900117428</v>
       </c>
       <c r="C25">
-        <v>22.96263727971722</v>
+        <v>21.0852259440179</v>
       </c>
       <c r="D25">
-        <v>21.69753727971722</v>
+        <v>20.1464259440179</v>
       </c>
       <c r="E25">
-        <v>0.5748999999999995</v>
+        <v>0.9012000000000002</v>
       </c>
       <c r="F25">
-        <v>7.504899999999999</v>
+        <v>7.8312</v>
       </c>
       <c r="G25">
         <v>8.77</v>
@@ -3337,45 +3337,45 @@
         <v>1.15</v>
       </c>
       <c r="M25">
-        <v>0.56887142</v>
+        <v>0.704808</v>
       </c>
       <c r="N25">
-        <v>0.5811285799999999</v>
+        <v>0.4451919999999999</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0.5811285799999999</v>
+        <v>0.4451919999999999</v>
       </c>
       <c r="Q25">
-        <v>1.15112858</v>
+        <v>1.015192</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09938560909243413</v>
+        <v>0.100090682896282</v>
       </c>
       <c r="T25">
-        <v>1.044483260053295</v>
+        <v>1.05822646084347</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.021546450690034</v>
+        <v>1.63165003802454</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09766891900117428</v>
+        <v>0.09811091900117427</v>
       </c>
       <c r="C26">
-        <v>21.0852259440179</v>
+        <v>20.58869914553524</v>
       </c>
       <c r="D26">
-        <v>20.1464259440179</v>
+        <v>19.97619914553524</v>
       </c>
       <c r="E26">
-        <v>0.9011999999999993</v>
+        <v>1.227499999999999</v>
       </c>
       <c r="F26">
-        <v>7.831199999999999</v>
+        <v>8.157499999999999</v>
       </c>
       <c r="G26">
         <v>8.77</v>
@@ -3419,28 +3419,28 @@
         <v>1.15</v>
       </c>
       <c r="M26">
-        <v>0.7048079999999999</v>
+        <v>0.7341749999999999</v>
       </c>
       <c r="N26">
-        <v>0.445192</v>
+        <v>0.415825</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0.445192</v>
+        <v>0.415825</v>
       </c>
       <c r="Q26">
-        <v>1.015192</v>
+        <v>0.9858250000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.100090682896282</v>
+        <v>0.1008145586682324</v>
       </c>
       <c r="T26">
-        <v>1.05822646084347</v>
+        <v>1.07233614698805</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.63165003802454</v>
+        <v>1.566384036503559</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09811091900117427</v>
+        <v>0.09855291900117429</v>
       </c>
       <c r="C27">
-        <v>20.58869914553524</v>
+        <v>20.09502489991046</v>
       </c>
       <c r="D27">
-        <v>19.97619914553524</v>
+        <v>19.80882489991046</v>
       </c>
       <c r="E27">
-        <v>1.227499999999999</v>
+        <v>1.553799999999999</v>
       </c>
       <c r="F27">
-        <v>8.157499999999999</v>
+        <v>8.483799999999999</v>
       </c>
       <c r="G27">
         <v>8.77</v>
@@ -3501,28 +3501,28 @@
         <v>1.15</v>
       </c>
       <c r="M27">
-        <v>0.7341749999999999</v>
+        <v>0.7635419999999998</v>
       </c>
       <c r="N27">
-        <v>0.415825</v>
+        <v>0.3864580000000001</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0.415825</v>
+        <v>0.3864580000000001</v>
       </c>
       <c r="Q27">
-        <v>0.9858250000000001</v>
+        <v>0.9564580000000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1008145586682324</v>
+        <v>0.1015579986502355</v>
       </c>
       <c r="T27">
-        <v>1.07233614698805</v>
+        <v>1.086827176001402</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.566384036503559</v>
+        <v>1.506138496638037</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09855291900117429</v>
+        <v>0.1143309190011743</v>
       </c>
       <c r="C28">
-        <v>20.09502489991046</v>
+        <v>15.20810257314096</v>
       </c>
       <c r="D28">
-        <v>19.80882489991046</v>
+        <v>15.24820257314096</v>
       </c>
       <c r="E28">
-        <v>1.553799999999999</v>
+        <v>1.880099999999999</v>
       </c>
       <c r="F28">
-        <v>8.483799999999999</v>
+        <v>8.810099999999998</v>
       </c>
       <c r="G28">
         <v>8.77</v>
@@ -3583,45 +3583,45 @@
         <v>1.15</v>
       </c>
       <c r="M28">
-        <v>0.7635419999999998</v>
+        <v>1.29332268</v>
       </c>
       <c r="N28">
-        <v>0.3864580000000001</v>
+        <v>-0.14332268</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P28">
-        <v>0.3864580000000001</v>
+        <v>-0.14332268</v>
       </c>
       <c r="Q28">
-        <v>0.9564580000000001</v>
+        <v>0.42667732</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1015579986502355</v>
+        <v>0.1023218068509237</v>
       </c>
       <c r="T28">
-        <v>1.086827176001402</v>
+        <v>1.10171521950827</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.506138496638037</v>
+        <v>0.889182582029722</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1143309190011743</v>
+        <v>0.1153409190011743</v>
       </c>
       <c r="C29">
-        <v>15.20810257314096</v>
+        <v>14.66034037764405</v>
       </c>
       <c r="D29">
-        <v>15.24820257314096</v>
+        <v>15.02674037764405</v>
       </c>
       <c r="E29">
-        <v>1.880099999999999</v>
+        <v>2.2064</v>
       </c>
       <c r="F29">
-        <v>8.810099999999998</v>
+        <v>9.1364</v>
       </c>
       <c r="G29">
         <v>8.77</v>
@@ -3665,28 +3665,28 @@
         <v>1.15</v>
       </c>
       <c r="M29">
-        <v>1.29332268</v>
+        <v>1.34122352</v>
       </c>
       <c r="N29">
-        <v>-0.14332268</v>
+        <v>-0.1912235200000003</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>-0.14332268</v>
+        <v>-0.1912235200000003</v>
       </c>
       <c r="Q29">
-        <v>0.42667732</v>
+        <v>0.3787764799999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1023218068509237</v>
+        <v>0.1031068319460754</v>
       </c>
       <c r="T29">
-        <v>1.10171521950827</v>
+        <v>1.117016819779218</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.889182582029722</v>
+        <v>0.8574260612429461</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1153409190011743</v>
+        <v>0.1163509190011743</v>
       </c>
       <c r="C30">
-        <v>14.66034037764405</v>
+        <v>14.11891904405564</v>
       </c>
       <c r="D30">
-        <v>15.02674037764405</v>
+        <v>14.81161904405564</v>
       </c>
       <c r="E30">
-        <v>2.2064</v>
+        <v>2.5327</v>
       </c>
       <c r="F30">
-        <v>9.1364</v>
+        <v>9.4627</v>
       </c>
       <c r="G30">
         <v>8.77</v>
@@ -3747,28 +3747,28 @@
         <v>1.15</v>
       </c>
       <c r="M30">
-        <v>1.34122352</v>
+        <v>1.38912436</v>
       </c>
       <c r="N30">
-        <v>-0.1912235200000003</v>
+        <v>-0.2391243600000001</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>-0.1912235200000003</v>
+        <v>-0.2391243600000001</v>
       </c>
       <c r="Q30">
-        <v>0.3787764799999997</v>
+        <v>0.3308756399999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1031068319460754</v>
+        <v>0.1039139704241891</v>
       </c>
       <c r="T30">
-        <v>1.117016819779218</v>
+        <v>1.132749451043715</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8574260612429461</v>
+        <v>0.827859645338017</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1163509190011743</v>
+        <v>0.1173609190011743</v>
       </c>
       <c r="C31">
-        <v>14.11891904405565</v>
+        <v>13.58357009047456</v>
       </c>
       <c r="D31">
-        <v>14.81161904405565</v>
+        <v>14.60257009047456</v>
       </c>
       <c r="E31">
-        <v>2.532699999999998</v>
+        <v>2.858999999999998</v>
       </c>
       <c r="F31">
-        <v>9.462699999999998</v>
+        <v>9.788999999999998</v>
       </c>
       <c r="G31">
         <v>8.77</v>
@@ -3829,28 +3829,28 @@
         <v>1.15</v>
       </c>
       <c r="M31">
-        <v>1.38912436</v>
+        <v>1.4370252</v>
       </c>
       <c r="N31">
-        <v>-0.2391243599999999</v>
+        <v>-0.2870252</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>-0.2391243599999999</v>
+        <v>-0.2870252</v>
       </c>
       <c r="Q31">
-        <v>0.3308756400000001</v>
+        <v>0.2829748000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1039139704241891</v>
+        <v>0.1047441700016775</v>
       </c>
       <c r="T31">
-        <v>1.132749451043714</v>
+        <v>1.148931586058625</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8278596453380171</v>
+        <v>0.8002643238267498</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1173609190011743</v>
+        <v>0.1351109190011743</v>
       </c>
       <c r="C32">
-        <v>13.58357009047456</v>
+        <v>10.3550984186937</v>
       </c>
       <c r="D32">
-        <v>14.60257009047456</v>
+        <v>11.7003984186937</v>
       </c>
       <c r="E32">
-        <v>2.858999999999998</v>
+        <v>3.185299999999998</v>
       </c>
       <c r="F32">
-        <v>9.788999999999998</v>
+        <v>10.1153</v>
       </c>
       <c r="G32">
         <v>8.77</v>
@@ -3911,45 +3911,45 @@
         <v>1.15</v>
       </c>
       <c r="M32">
-        <v>1.4370252</v>
+        <v>2.031152239999999</v>
       </c>
       <c r="N32">
-        <v>-0.2870252</v>
+        <v>-0.8811522399999996</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-0.2870252</v>
+        <v>-0.8811522399999996</v>
       </c>
       <c r="Q32">
-        <v>0.2829748000000001</v>
+        <v>-0.3111522399999995</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1047441700016775</v>
+        <v>0.1055984333350352</v>
       </c>
       <c r="T32">
-        <v>1.148931586058625</v>
+        <v>1.165582768465271</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8002643238267498</v>
+        <v>0.5661810953176016</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1351109190011743</v>
+        <v>0.1366609190011743</v>
       </c>
       <c r="C33">
-        <v>10.3550984186937</v>
+        <v>9.829200860707951</v>
       </c>
       <c r="D33">
-        <v>11.7003984186937</v>
+        <v>11.50080086070795</v>
       </c>
       <c r="E33">
-        <v>3.185299999999998</v>
+        <v>3.5116</v>
       </c>
       <c r="F33">
-        <v>10.1153</v>
+        <v>10.4416</v>
       </c>
       <c r="G33">
         <v>8.77</v>
@@ -3993,28 +3993,28 @@
         <v>1.15</v>
       </c>
       <c r="M33">
-        <v>2.031152239999999</v>
+        <v>2.09667328</v>
       </c>
       <c r="N33">
-        <v>-0.8811522399999996</v>
+        <v>-0.9466732800000002</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-0.8811522399999996</v>
+        <v>-0.9466732800000002</v>
       </c>
       <c r="Q33">
-        <v>-0.3111522399999995</v>
+        <v>-0.3766732800000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1055984333350352</v>
+        <v>0.1064778220605504</v>
       </c>
       <c r="T33">
-        <v>1.165582768465271</v>
+        <v>1.182723691530937</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5661810953176016</v>
+        <v>0.5484879360889265</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1366609190011743</v>
+        <v>0.1382109190011743</v>
       </c>
       <c r="C34">
-        <v>9.829200860707951</v>
+        <v>9.309998966356366</v>
       </c>
       <c r="D34">
-        <v>11.50080086070795</v>
+        <v>11.30789896635637</v>
       </c>
       <c r="E34">
-        <v>3.5116</v>
+        <v>3.837899999999999</v>
       </c>
       <c r="F34">
-        <v>10.4416</v>
+        <v>10.7679</v>
       </c>
       <c r="G34">
         <v>8.77</v>
@@ -4075,28 +4075,28 @@
         <v>1.15</v>
       </c>
       <c r="M34">
-        <v>2.09667328</v>
+        <v>2.16219432</v>
       </c>
       <c r="N34">
-        <v>-0.9466732800000002</v>
+        <v>-1.01219432</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-0.9466732800000002</v>
+        <v>-1.01219432</v>
       </c>
       <c r="Q34">
-        <v>-0.3766732800000001</v>
+        <v>-0.4421943199999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064778220605504</v>
+        <v>0.1073834611957825</v>
       </c>
       <c r="T34">
-        <v>1.182723691530937</v>
+        <v>1.200376283941847</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5484879360889265</v>
+        <v>0.5318670895407773</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1382109190011743</v>
+        <v>0.1397609190011743</v>
       </c>
       <c r="C35">
-        <v>9.309998966356366</v>
+        <v>8.797161376216009</v>
       </c>
       <c r="D35">
-        <v>11.30789896635637</v>
+        <v>11.12136137621601</v>
       </c>
       <c r="E35">
-        <v>3.837899999999999</v>
+        <v>4.164199999999999</v>
       </c>
       <c r="F35">
-        <v>10.7679</v>
+        <v>11.0942</v>
       </c>
       <c r="G35">
         <v>8.77</v>
@@ -4157,28 +4157,28 @@
         <v>1.15</v>
       </c>
       <c r="M35">
-        <v>2.16219432</v>
+        <v>2.22771536</v>
       </c>
       <c r="N35">
-        <v>-1.01219432</v>
+        <v>-1.07771536</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-1.01219432</v>
+        <v>-1.07771536</v>
       </c>
       <c r="Q35">
-        <v>-0.4421943199999998</v>
+        <v>-0.5077153599999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1073834611957825</v>
+        <v>0.1083165439411732</v>
       </c>
       <c r="T35">
-        <v>1.200376283941847</v>
+        <v>1.218563803395511</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5318670895407773</v>
+        <v>0.5162239398484014</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1397609190011743</v>
+        <v>0.1413109190011743</v>
       </c>
       <c r="C36">
-        <v>8.797161376216009</v>
+        <v>8.29037824074411</v>
       </c>
       <c r="D36">
-        <v>11.12136137621601</v>
+        <v>10.94087824074411</v>
       </c>
       <c r="E36">
-        <v>4.164199999999999</v>
+        <v>4.490499999999999</v>
       </c>
       <c r="F36">
-        <v>11.0942</v>
+        <v>11.4205</v>
       </c>
       <c r="G36">
         <v>8.77</v>
@@ -4239,28 +4239,28 @@
         <v>1.15</v>
       </c>
       <c r="M36">
-        <v>2.22771536</v>
+        <v>2.2932364</v>
       </c>
       <c r="N36">
-        <v>-1.07771536</v>
+        <v>-1.1432364</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-1.07771536</v>
+        <v>-1.1432364</v>
       </c>
       <c r="Q36">
-        <v>-0.5077153599999999</v>
+        <v>-0.5732363999999996</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1083165439411732</v>
+        <v>0.1092783369248835</v>
       </c>
       <c r="T36">
-        <v>1.218563803395511</v>
+        <v>1.237310938832365</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5162239398484014</v>
+        <v>0.5014746844241615</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1413109190011743</v>
+        <v>0.1554609190011743</v>
       </c>
       <c r="C37">
-        <v>8.29037824074411</v>
+        <v>6.55233166305154</v>
       </c>
       <c r="D37">
-        <v>10.94087824074411</v>
+        <v>9.529131663051539</v>
       </c>
       <c r="E37">
-        <v>4.490499999999999</v>
+        <v>4.816800000000001</v>
       </c>
       <c r="F37">
-        <v>11.4205</v>
+        <v>11.7468</v>
       </c>
       <c r="G37">
         <v>8.77</v>
@@ -4321,45 +4321,45 @@
         <v>1.15</v>
       </c>
       <c r="M37">
-        <v>2.2932364</v>
+        <v>2.76989544</v>
       </c>
       <c r="N37">
-        <v>-1.1432364</v>
+        <v>-1.61989544</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-1.1432364</v>
+        <v>-1.61989544</v>
       </c>
       <c r="Q37">
-        <v>-0.5732363999999996</v>
+        <v>-1.04989544</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1092783369248835</v>
+        <v>0.1102701859393348</v>
       </c>
       <c r="T37">
-        <v>1.237310938832365</v>
+        <v>1.256643922251621</v>
       </c>
       <c r="U37">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.5014746844241615</v>
+        <v>0.4151781267238015</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1554609190011743</v>
+        <v>0.1573609190011743</v>
       </c>
       <c r="C38">
-        <v>6.552331663051541</v>
+        <v>6.063740510182791</v>
       </c>
       <c r="D38">
-        <v>9.529131663051539</v>
+        <v>9.36684051018279</v>
       </c>
       <c r="E38">
-        <v>4.816799999999999</v>
+        <v>5.143099999999999</v>
       </c>
       <c r="F38">
-        <v>11.7468</v>
+        <v>12.0731</v>
       </c>
       <c r="G38">
         <v>8.77</v>
@@ -4403,28 +4403,28 @@
         <v>1.15</v>
       </c>
       <c r="M38">
-        <v>2.76989544</v>
+        <v>2.84683698</v>
       </c>
       <c r="N38">
-        <v>-1.61989544</v>
+        <v>-1.69683698</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-1.61989544</v>
+        <v>-1.69683698</v>
       </c>
       <c r="Q38">
-        <v>-1.04989544</v>
+        <v>-1.12683698</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1102701859393348</v>
+        <v>0.1112935222240862</v>
       </c>
       <c r="T38">
-        <v>1.256643922251621</v>
+        <v>1.27659065117625</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4151781267238015</v>
+        <v>0.403957096271807</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1573609190011743</v>
+        <v>0.1592609190011743</v>
       </c>
       <c r="C39">
-        <v>6.063740510182791</v>
+        <v>5.58058476526182</v>
       </c>
       <c r="D39">
-        <v>9.36684051018279</v>
+        <v>9.209984765261821</v>
       </c>
       <c r="E39">
-        <v>5.143099999999999</v>
+        <v>5.469399999999998</v>
       </c>
       <c r="F39">
-        <v>12.0731</v>
+        <v>12.3994</v>
       </c>
       <c r="G39">
         <v>8.77</v>
@@ -4485,28 +4485,28 @@
         <v>1.15</v>
       </c>
       <c r="M39">
-        <v>2.84683698</v>
+        <v>2.923778519999999</v>
       </c>
       <c r="N39">
-        <v>-1.69683698</v>
+        <v>-1.77377852</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-1.69683698</v>
+        <v>-1.77377852</v>
       </c>
       <c r="Q39">
-        <v>-1.12683698</v>
+        <v>-1.20377852</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1112935222240862</v>
+        <v>0.1123498693567327</v>
       </c>
       <c r="T39">
-        <v>1.27659065117625</v>
+        <v>1.297180822969415</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.403957096271807</v>
+        <v>0.3933266463699173</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1592609190011743</v>
+        <v>0.1611609190011743</v>
       </c>
       <c r="C40">
-        <v>5.58058476526182</v>
+        <v>5.102595863981316</v>
       </c>
       <c r="D40">
-        <v>9.209984765261821</v>
+        <v>9.058295863981314</v>
       </c>
       <c r="E40">
-        <v>5.469399999999998</v>
+        <v>5.795699999999998</v>
       </c>
       <c r="F40">
-        <v>12.3994</v>
+        <v>12.7257</v>
       </c>
       <c r="G40">
         <v>8.77</v>
@@ -4567,28 +4567,28 @@
         <v>1.15</v>
       </c>
       <c r="M40">
-        <v>2.923778519999999</v>
+        <v>3.000720059999999</v>
       </c>
       <c r="N40">
-        <v>-1.77377852</v>
+        <v>-1.85072006</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-1.77377852</v>
+        <v>-1.85072006</v>
       </c>
       <c r="Q40">
-        <v>-1.20377852</v>
+        <v>-1.280720059999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1123498693567327</v>
+        <v>0.1134408508215972</v>
       </c>
       <c r="T40">
-        <v>1.297180822969415</v>
+        <v>1.318446082362356</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3933266463699173</v>
+        <v>0.3832413477450476</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1611609190011743</v>
+        <v>0.1630609190011743</v>
       </c>
       <c r="C41">
-        <v>5.102595863981316</v>
+        <v>4.629522648419254</v>
       </c>
       <c r="D41">
-        <v>9.058295863981314</v>
+        <v>8.911522648419252</v>
       </c>
       <c r="E41">
-        <v>5.795699999999998</v>
+        <v>6.122</v>
       </c>
       <c r="F41">
-        <v>12.7257</v>
+        <v>13.052</v>
       </c>
       <c r="G41">
         <v>8.77</v>
@@ -4649,28 +4649,28 @@
         <v>1.15</v>
       </c>
       <c r="M41">
-        <v>3.000720059999999</v>
+        <v>3.0776616</v>
       </c>
       <c r="N41">
-        <v>-1.85072006</v>
+        <v>-1.9276616</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-1.85072006</v>
+        <v>-1.9276616</v>
       </c>
       <c r="Q41">
-        <v>-1.280720059999999</v>
+        <v>-1.3576616</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1134408508215972</v>
+        <v>0.1145681983352905</v>
       </c>
       <c r="T41">
-        <v>1.318446082362356</v>
+        <v>1.340420183735062</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3832413477450476</v>
+        <v>0.3736603140514214</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1630609190011743</v>
+        <v>0.1649609190011743</v>
       </c>
       <c r="C42">
-        <v>4.629522648419254</v>
+        <v>4.161129979330074</v>
       </c>
       <c r="D42">
-        <v>8.911522648419252</v>
+        <v>8.769429979330075</v>
       </c>
       <c r="E42">
-        <v>6.122</v>
+        <v>6.4483</v>
       </c>
       <c r="F42">
-        <v>13.052</v>
+        <v>13.3783</v>
       </c>
       <c r="G42">
         <v>8.77</v>
@@ -4731,28 +4731,28 @@
         <v>1.15</v>
       </c>
       <c r="M42">
-        <v>3.0776616</v>
+        <v>3.15460314</v>
       </c>
       <c r="N42">
-        <v>-1.9276616</v>
+        <v>-2.00460314</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-1.9276616</v>
+        <v>-2.00460314</v>
       </c>
       <c r="Q42">
-        <v>-1.3576616</v>
+        <v>-1.43460314</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1145681983352905</v>
+        <v>0.1157337610189395</v>
       </c>
       <c r="T42">
-        <v>1.340420183735062</v>
+        <v>1.363139169900063</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3736603140514214</v>
+        <v>0.3645466478550452</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1649609190011743</v>
+        <v>0.1668609190011743</v>
       </c>
       <c r="C43">
-        <v>4.161129979330074</v>
+        <v>3.697197479112845</v>
       </c>
       <c r="D43">
-        <v>8.769429979330075</v>
+        <v>8.631797479112844</v>
       </c>
       <c r="E43">
-        <v>6.4483</v>
+        <v>6.7746</v>
       </c>
       <c r="F43">
-        <v>13.3783</v>
+        <v>13.7046</v>
       </c>
       <c r="G43">
         <v>8.77</v>
@@ -4813,28 +4813,28 @@
         <v>1.15</v>
       </c>
       <c r="M43">
-        <v>3.15460314</v>
+        <v>3.23154468</v>
       </c>
       <c r="N43">
-        <v>-2.00460314</v>
+        <v>-2.08154468</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-2.00460314</v>
+        <v>-2.08154468</v>
       </c>
       <c r="Q43">
-        <v>-1.43460314</v>
+        <v>-1.51154468</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1157337610189395</v>
+        <v>0.116939515519266</v>
       </c>
       <c r="T43">
-        <v>1.363139169900063</v>
+        <v>1.386641569381099</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3645466478550452</v>
+        <v>0.3558669657632585</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1668609190011743</v>
+        <v>0.1687609190011743</v>
       </c>
       <c r="C44">
-        <v>3.697197479112846</v>
+        <v>3.23751839132189</v>
       </c>
       <c r="D44">
-        <v>8.631797479112844</v>
+        <v>8.498418391321886</v>
       </c>
       <c r="E44">
-        <v>6.774599999999998</v>
+        <v>7.100899999999998</v>
       </c>
       <c r="F44">
-        <v>13.7046</v>
+        <v>14.0309</v>
       </c>
       <c r="G44">
         <v>8.77</v>
@@ -4895,28 +4895,28 @@
         <v>1.15</v>
       </c>
       <c r="M44">
-        <v>3.231544679999999</v>
+        <v>3.308486219999999</v>
       </c>
       <c r="N44">
-        <v>-2.081544679999999</v>
+        <v>-2.158486219999999</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-2.081544679999999</v>
+        <v>-2.158486219999999</v>
       </c>
       <c r="Q44">
-        <v>-1.511544679999999</v>
+        <v>-1.588486219999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.116939515519266</v>
+        <v>0.1181875771950426</v>
       </c>
       <c r="T44">
-        <v>1.386641569381099</v>
+        <v>1.41096861445796</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3558669657632585</v>
+        <v>0.3475909898152757</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1687609190011743</v>
+        <v>0.1706609190011743</v>
       </c>
       <c r="C45">
-        <v>3.23751839132189</v>
+        <v>2.781898544305868</v>
       </c>
       <c r="D45">
-        <v>8.498418391321886</v>
+        <v>8.369098544305865</v>
       </c>
       <c r="E45">
-        <v>7.100899999999998</v>
+        <v>7.427199999999999</v>
       </c>
       <c r="F45">
-        <v>14.0309</v>
+        <v>14.3572</v>
       </c>
       <c r="G45">
         <v>8.77</v>
@@ -4977,28 +4977,28 @@
         <v>1.15</v>
       </c>
       <c r="M45">
-        <v>3.308486219999999</v>
+        <v>3.38542776</v>
       </c>
       <c r="N45">
-        <v>-2.158486219999999</v>
+        <v>-2.23542776</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-2.158486219999999</v>
+        <v>-2.23542776</v>
       </c>
       <c r="Q45">
-        <v>-1.588486219999999</v>
+        <v>-1.66542776</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1181875771950426</v>
+        <v>0.1194802125020969</v>
       </c>
       <c r="T45">
-        <v>1.41096861445796</v>
+        <v>1.436164482573281</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3475909898152757</v>
+        <v>0.3396911945922012</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1706609190011743</v>
+        <v>0.1725609190011743</v>
       </c>
       <c r="C46">
-        <v>2.781898544305868</v>
+        <v>2.330155408050015</v>
       </c>
       <c r="D46">
-        <v>8.369098544305865</v>
+        <v>8.243655408050014</v>
       </c>
       <c r="E46">
-        <v>7.427199999999999</v>
+        <v>7.753499999999999</v>
       </c>
       <c r="F46">
-        <v>14.3572</v>
+        <v>14.6835</v>
       </c>
       <c r="G46">
         <v>8.77</v>
@@ -5059,28 +5059,28 @@
         <v>1.15</v>
       </c>
       <c r="M46">
-        <v>3.38542776</v>
+        <v>3.4623693</v>
       </c>
       <c r="N46">
-        <v>-2.23542776</v>
+        <v>-2.3123693</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-2.23542776</v>
+        <v>-2.3123693</v>
       </c>
       <c r="Q46">
-        <v>-1.66542776</v>
+        <v>-1.7423693</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1194802125020969</v>
+        <v>0.1208198527294078</v>
       </c>
       <c r="T46">
-        <v>1.436164482573281</v>
+        <v>1.462276564074613</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3396911945922012</v>
+        <v>0.3321425013790412</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1725609190011743</v>
+        <v>0.1744609190011743</v>
       </c>
       <c r="C47">
-        <v>2.330155408050015</v>
+        <v>1.88211723458685</v>
       </c>
       <c r="D47">
-        <v>8.243655408050014</v>
+        <v>8.121917234586851</v>
       </c>
       <c r="E47">
-        <v>7.753499999999999</v>
+        <v>8.079799999999999</v>
       </c>
       <c r="F47">
-        <v>14.6835</v>
+        <v>15.0098</v>
       </c>
       <c r="G47">
         <v>8.77</v>
@@ -5141,28 +5141,28 @@
         <v>1.15</v>
       </c>
       <c r="M47">
-        <v>3.4623693</v>
+        <v>3.53931084</v>
       </c>
       <c r="N47">
-        <v>-2.3123693</v>
+        <v>-2.38931084</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-2.3123693</v>
+        <v>-2.38931084</v>
       </c>
       <c r="Q47">
-        <v>-1.7423693</v>
+        <v>-1.81931084</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1208198527294078</v>
+        <v>0.1222091092614339</v>
       </c>
       <c r="T47">
-        <v>1.462276564074613</v>
+        <v>1.489355759705625</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3321425013790412</v>
+        <v>0.3249220122186273</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1744609190011743</v>
+        <v>0.1763609190011743</v>
       </c>
       <c r="C48">
-        <v>1.88211723458685</v>
+        <v>1.437622273462413</v>
       </c>
       <c r="D48">
-        <v>8.121917234586851</v>
+        <v>8.003722273462412</v>
       </c>
       <c r="E48">
-        <v>8.079799999999999</v>
+        <v>8.406099999999999</v>
       </c>
       <c r="F48">
-        <v>15.0098</v>
+        <v>15.3361</v>
       </c>
       <c r="G48">
         <v>8.77</v>
@@ -5223,28 +5223,28 @@
         <v>1.15</v>
       </c>
       <c r="M48">
-        <v>3.53931084</v>
+        <v>3.61625238</v>
       </c>
       <c r="N48">
-        <v>-2.38931084</v>
+        <v>-2.46625238</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-2.38931084</v>
+        <v>-2.46625238</v>
       </c>
       <c r="Q48">
-        <v>-1.81931084</v>
+        <v>-1.89625238</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1222091092614339</v>
+        <v>0.1236507905682534</v>
       </c>
       <c r="T48">
-        <v>1.489355759705625</v>
+        <v>1.517456811775542</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3249220122186273</v>
+        <v>0.3180087779161033</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1763609190011743</v>
+        <v>0.1782609190011743</v>
       </c>
       <c r="C49">
-        <v>1.437622273462413</v>
+        <v>0.9965180547219088</v>
       </c>
       <c r="D49">
-        <v>8.003722273462412</v>
+        <v>7.888918054721909</v>
       </c>
       <c r="E49">
-        <v>8.406099999999999</v>
+        <v>8.7324</v>
       </c>
       <c r="F49">
-        <v>15.3361</v>
+        <v>15.6624</v>
       </c>
       <c r="G49">
         <v>8.77</v>
@@ -5305,28 +5305,28 @@
         <v>1.15</v>
       </c>
       <c r="M49">
-        <v>3.61625238</v>
+        <v>3.69319392</v>
       </c>
       <c r="N49">
-        <v>-2.46625238</v>
+        <v>-2.54319392</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-2.46625238</v>
+        <v>-2.54319392</v>
       </c>
       <c r="Q49">
-        <v>-1.89625238</v>
+        <v>-1.97319392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1236507905682534</v>
+        <v>0.1251479211561044</v>
       </c>
       <c r="T49">
-        <v>1.517456811775542</v>
+        <v>1.546638673540456</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3180087779161033</v>
+        <v>0.3113835950428511</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1782609190011743</v>
+        <v>0.1801609190011743</v>
       </c>
       <c r="C50">
-        <v>0.9965180547219106</v>
+        <v>0.5586607327312763</v>
       </c>
       <c r="D50">
-        <v>7.888918054721909</v>
+        <v>7.777360732731275</v>
       </c>
       <c r="E50">
-        <v>8.732399999999998</v>
+        <v>9.058699999999998</v>
       </c>
       <c r="F50">
-        <v>15.6624</v>
+        <v>15.9887</v>
       </c>
       <c r="G50">
         <v>8.77</v>
@@ -5387,28 +5387,28 @@
         <v>1.15</v>
       </c>
       <c r="M50">
-        <v>3.69319392</v>
+        <v>3.77013546</v>
       </c>
       <c r="N50">
-        <v>-2.54319392</v>
+        <v>-2.62013546</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-2.54319392</v>
+        <v>-2.62013546</v>
       </c>
       <c r="Q50">
-        <v>-1.97319392</v>
+        <v>-2.05013546</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1251479211561044</v>
+        <v>0.1267037627474006</v>
       </c>
       <c r="T50">
-        <v>1.546638673540456</v>
+        <v>1.576964922041249</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3113835950428512</v>
+        <v>0.3050288277970786</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1801609190011743</v>
+        <v>0.1820609190011743</v>
       </c>
       <c r="C51">
-        <v>0.5586607327312763</v>
+        <v>0.1239144848965452</v>
       </c>
       <c r="D51">
-        <v>7.777360732731275</v>
+        <v>7.668914484896545</v>
       </c>
       <c r="E51">
-        <v>9.058699999999998</v>
+        <v>9.384999999999998</v>
       </c>
       <c r="F51">
-        <v>15.9887</v>
+        <v>16.315</v>
       </c>
       <c r="G51">
         <v>8.77</v>
@@ -5469,28 +5469,28 @@
         <v>1.15</v>
       </c>
       <c r="M51">
-        <v>3.77013546</v>
+        <v>3.847077</v>
       </c>
       <c r="N51">
-        <v>-2.62013546</v>
+        <v>-2.697077</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-2.62013546</v>
+        <v>-2.697077</v>
       </c>
       <c r="Q51">
-        <v>-2.05013546</v>
+        <v>-2.127077</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1267037627474006</v>
+        <v>0.1283218380023486</v>
       </c>
       <c r="T51">
-        <v>1.576964922041249</v>
+        <v>1.608504220482075</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3050288277970786</v>
+        <v>0.2989282512411371</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1820609190011743</v>
+        <v>0.1839609190011743</v>
       </c>
       <c r="C52">
-        <v>0.1239144848965452</v>
+        <v>-0.3078490400035712</v>
       </c>
       <c r="D52">
-        <v>7.668914484896545</v>
+        <v>7.563450959996427</v>
       </c>
       <c r="E52">
-        <v>9.384999999999998</v>
+        <v>9.711299999999998</v>
       </c>
       <c r="F52">
-        <v>16.315</v>
+        <v>16.6413</v>
       </c>
       <c r="G52">
         <v>8.77</v>
@@ -5551,28 +5551,28 @@
         <v>1.15</v>
       </c>
       <c r="M52">
-        <v>3.847077</v>
+        <v>3.92401854</v>
       </c>
       <c r="N52">
-        <v>-2.697077</v>
+        <v>-2.77401854</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-2.697077</v>
+        <v>-2.77401854</v>
       </c>
       <c r="Q52">
-        <v>-2.127077</v>
+        <v>-2.20401854</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1283218380023486</v>
+        <v>0.1300059571452536</v>
       </c>
       <c r="T52">
-        <v>1.608504220482075</v>
+        <v>1.641330837226607</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2989282512411371</v>
+        <v>0.293066912981507</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1839609190011743</v>
+        <v>0.1858609190011743</v>
       </c>
       <c r="C53">
-        <v>-0.3078490400035712</v>
+        <v>-0.7367512285831879</v>
       </c>
       <c r="D53">
-        <v>7.563450959996427</v>
+        <v>7.460848771416808</v>
       </c>
       <c r="E53">
-        <v>9.711299999999998</v>
+        <v>10.0376</v>
       </c>
       <c r="F53">
-        <v>16.6413</v>
+        <v>16.9676</v>
       </c>
       <c r="G53">
         <v>8.77</v>
@@ -5633,28 +5633,28 @@
         <v>1.15</v>
       </c>
       <c r="M53">
-        <v>3.92401854</v>
+        <v>4.00096008</v>
       </c>
       <c r="N53">
-        <v>-2.77401854</v>
+        <v>-2.85096008</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-2.77401854</v>
+        <v>-2.85096008</v>
       </c>
       <c r="Q53">
-        <v>-2.20401854</v>
+        <v>-2.28096008</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1300059571452536</v>
+        <v>0.1317602479191131</v>
       </c>
       <c r="T53">
-        <v>1.641330837226607</v>
+        <v>1.675525229668828</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.293066912981507</v>
+        <v>0.2874310108087856</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1858609190011743</v>
+        <v>0.1877609190011743</v>
       </c>
       <c r="C54">
-        <v>-0.7367512285831879</v>
+        <v>-1.162906968919547</v>
       </c>
       <c r="D54">
-        <v>7.460848771416808</v>
+        <v>7.360993031080451</v>
       </c>
       <c r="E54">
-        <v>10.0376</v>
+        <v>10.3639</v>
       </c>
       <c r="F54">
-        <v>16.9676</v>
+        <v>17.2939</v>
       </c>
       <c r="G54">
         <v>8.77</v>
@@ -5715,28 +5715,28 @@
         <v>1.15</v>
       </c>
       <c r="M54">
-        <v>4.00096008</v>
+        <v>4.07790162</v>
       </c>
       <c r="N54">
-        <v>-2.85096008</v>
+        <v>-2.92790162</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-2.85096008</v>
+        <v>-2.92790162</v>
       </c>
       <c r="Q54">
-        <v>-2.28096008</v>
+        <v>-2.35790162</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1317602479191131</v>
+        <v>0.1335891893642006</v>
       </c>
       <c r="T54">
-        <v>1.675525229668828</v>
+        <v>1.711174702640505</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2874310108087856</v>
+        <v>0.282007784189752</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1877609190011743</v>
+        <v>0.1896609190011743</v>
       </c>
       <c r="C55">
-        <v>-1.162906968919547</v>
+        <v>-1.586425079690397</v>
       </c>
       <c r="D55">
-        <v>7.360993031080451</v>
+        <v>7.2637749203096</v>
       </c>
       <c r="E55">
-        <v>10.3639</v>
+        <v>10.6902</v>
       </c>
       <c r="F55">
-        <v>17.2939</v>
+        <v>17.6202</v>
       </c>
       <c r="G55">
         <v>8.77</v>
@@ -5797,28 +5797,28 @@
         <v>1.15</v>
       </c>
       <c r="M55">
-        <v>4.07790162</v>
+        <v>4.15484316</v>
       </c>
       <c r="N55">
-        <v>-2.92790162</v>
+        <v>-3.00484316</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-2.92790162</v>
+        <v>-3.00484316</v>
       </c>
       <c r="Q55">
-        <v>-2.35790162</v>
+        <v>-2.43484316</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1335891893642006</v>
+        <v>0.1354976500025528</v>
       </c>
       <c r="T55">
-        <v>1.711174702640505</v>
+        <v>1.748374152697907</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.282007784189752</v>
+        <v>0.2767854178158677</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1896609190011743</v>
+        <v>0.1915609190011743</v>
       </c>
       <c r="C56">
-        <v>-1.586425079690397</v>
+        <v>-2.007408705748475</v>
       </c>
       <c r="D56">
-        <v>7.2637749203096</v>
+        <v>7.169091294251525</v>
       </c>
       <c r="E56">
-        <v>10.6902</v>
+        <v>11.0165</v>
       </c>
       <c r="F56">
-        <v>17.6202</v>
+        <v>17.9465</v>
       </c>
       <c r="G56">
         <v>8.77</v>
@@ -5879,28 +5879,28 @@
         <v>1.15</v>
       </c>
       <c r="M56">
-        <v>4.15484316</v>
+        <v>4.2317847</v>
       </c>
       <c r="N56">
-        <v>-3.00484316</v>
+        <v>-3.0817847</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-3.00484316</v>
+        <v>-3.0817847</v>
       </c>
       <c r="Q56">
-        <v>-2.43484316</v>
+        <v>-2.511784700000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1354976500025528</v>
+        <v>0.1374909311137206</v>
       </c>
       <c r="T56">
-        <v>1.748374152697907</v>
+        <v>1.78722691164675</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2767854178158677</v>
+        <v>0.271752955673761</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1915609190011743</v>
+        <v>0.1934609190011743</v>
       </c>
       <c r="C57">
-        <v>-2.007408705748475</v>
+        <v>-2.425955683156015</v>
       </c>
       <c r="D57">
-        <v>7.169091294251525</v>
+        <v>7.076844316843985</v>
       </c>
       <c r="E57">
-        <v>11.0165</v>
+        <v>11.3428</v>
       </c>
       <c r="F57">
-        <v>17.9465</v>
+        <v>18.2728</v>
       </c>
       <c r="G57">
         <v>8.77</v>
@@ -5961,28 +5961,28 @@
         <v>1.15</v>
       </c>
       <c r="M57">
-        <v>4.2317847</v>
+        <v>4.30872624</v>
       </c>
       <c r="N57">
-        <v>-3.0817847</v>
+        <v>-3.15872624</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-3.0817847</v>
+        <v>-3.15872624</v>
       </c>
       <c r="Q57">
-        <v>-2.511784700000001</v>
+        <v>-2.588726240000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1374909311137206</v>
+        <v>0.1395748159117597</v>
       </c>
       <c r="T57">
-        <v>1.78722691164675</v>
+        <v>1.827845705093267</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.271752955673761</v>
+        <v>0.2669002243224438</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1934609190011743</v>
+        <v>0.1953609190011743</v>
       </c>
       <c r="C58">
-        <v>-2.425955683156015</v>
+        <v>-2.842158876395274</v>
       </c>
       <c r="D58">
-        <v>7.076844316843985</v>
+        <v>6.986941123604726</v>
       </c>
       <c r="E58">
-        <v>11.3428</v>
+        <v>11.6691</v>
       </c>
       <c r="F58">
-        <v>18.2728</v>
+        <v>18.5991</v>
       </c>
       <c r="G58">
         <v>8.77</v>
@@ -6043,28 +6043,28 @@
         <v>1.15</v>
       </c>
       <c r="M58">
-        <v>4.30872624</v>
+        <v>4.38566778</v>
       </c>
       <c r="N58">
-        <v>-3.15872624</v>
+        <v>-3.23566778</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-3.15872624</v>
+        <v>-3.23566778</v>
       </c>
       <c r="Q58">
-        <v>-2.588726240000001</v>
+        <v>-2.665667780000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1395748159117597</v>
+        <v>0.1417556255841263</v>
       </c>
       <c r="T58">
-        <v>1.827845705093267</v>
+        <v>1.870353744746599</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2669002243224438</v>
+        <v>0.2622177642466115</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1953609190011743</v>
+        <v>0.1972609190011743</v>
       </c>
       <c r="C59">
-        <v>-2.842158876395274</v>
+        <v>-3.256106490198185</v>
       </c>
       <c r="D59">
-        <v>6.986941123604726</v>
+        <v>6.899293509801815</v>
       </c>
       <c r="E59">
-        <v>11.6691</v>
+        <v>11.9954</v>
       </c>
       <c r="F59">
-        <v>18.5991</v>
+        <v>18.9254</v>
       </c>
       <c r="G59">
         <v>8.77</v>
@@ -6125,28 +6125,28 @@
         <v>1.15</v>
       </c>
       <c r="M59">
-        <v>4.38566778</v>
+        <v>4.46260932</v>
       </c>
       <c r="N59">
-        <v>-3.23566778</v>
+        <v>-3.31260932</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-3.23566778</v>
+        <v>-3.31260932</v>
       </c>
       <c r="Q59">
-        <v>-2.665667780000001</v>
+        <v>-2.742609320000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1417556255841263</v>
+        <v>0.1440402833361293</v>
       </c>
       <c r="T59">
-        <v>1.870353744746599</v>
+        <v>1.914885976764375</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2622177642466115</v>
+        <v>0.257696768311325</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1972609190011743</v>
+        <v>0.1991609190011743</v>
       </c>
       <c r="C60">
-        <v>-3.256106490198178</v>
+        <v>-3.667882358196358</v>
       </c>
       <c r="D60">
-        <v>6.899293509801818</v>
+        <v>6.813817641803639</v>
       </c>
       <c r="E60">
-        <v>11.9954</v>
+        <v>12.3217</v>
       </c>
       <c r="F60">
-        <v>18.9254</v>
+        <v>19.2517</v>
       </c>
       <c r="G60">
         <v>8.77</v>
@@ -6207,28 +6207,28 @@
         <v>1.15</v>
       </c>
       <c r="M60">
-        <v>4.462609319999999</v>
+        <v>4.539550859999999</v>
       </c>
       <c r="N60">
-        <v>-3.31260932</v>
+        <v>-3.389550859999999</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-3.31260932</v>
+        <v>-3.389550859999999</v>
       </c>
       <c r="Q60">
-        <v>-2.74260932</v>
+        <v>-2.81955086</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1440402833361292</v>
+        <v>0.1464363878077421</v>
       </c>
       <c r="T60">
-        <v>1.914885976764374</v>
+        <v>1.961590512783017</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2576967683113252</v>
+        <v>0.2533290264755399</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1991609190011743</v>
+        <v>0.2010609190011743</v>
       </c>
       <c r="C61">
-        <v>-3.667882358196358</v>
+        <v>-4.077566210377014</v>
       </c>
       <c r="D61">
-        <v>6.813817641803639</v>
+        <v>6.730433789622981</v>
       </c>
       <c r="E61">
-        <v>12.3217</v>
+        <v>12.648</v>
       </c>
       <c r="F61">
-        <v>19.2517</v>
+        <v>19.578</v>
       </c>
       <c r="G61">
         <v>8.77</v>
@@ -6289,28 +6289,28 @@
         <v>1.15</v>
       </c>
       <c r="M61">
-        <v>4.539550859999999</v>
+        <v>4.616492399999999</v>
       </c>
       <c r="N61">
-        <v>-3.389550859999999</v>
+        <v>-3.466492399999999</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-3.389550859999999</v>
+        <v>-3.466492399999999</v>
       </c>
       <c r="Q61">
-        <v>-2.81955086</v>
+        <v>-2.8964924</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1464363878077421</v>
+        <v>0.1489522975029357</v>
       </c>
       <c r="T61">
-        <v>1.961590512783017</v>
+        <v>2.010630275602593</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2533290264755399</v>
+        <v>0.2491068760342809</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2010609190011743</v>
+        <v>0.2029609190011743</v>
       </c>
       <c r="C62">
-        <v>-4.077566210377014</v>
+        <v>-4.485233921138416</v>
       </c>
       <c r="D62">
-        <v>6.730433789622981</v>
+        <v>6.64906607886158</v>
       </c>
       <c r="E62">
-        <v>12.648</v>
+        <v>12.9743</v>
       </c>
       <c r="F62">
-        <v>19.578</v>
+        <v>19.9043</v>
       </c>
       <c r="G62">
         <v>8.77</v>
@@ -6371,28 +6371,28 @@
         <v>1.15</v>
       </c>
       <c r="M62">
-        <v>4.616492399999999</v>
+        <v>4.693433939999999</v>
       </c>
       <c r="N62">
-        <v>-3.466492399999999</v>
+        <v>-3.543433939999999</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-3.466492399999999</v>
+        <v>-3.543433939999999</v>
       </c>
       <c r="Q62">
-        <v>-2.8964924</v>
+        <v>-2.97343394</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1489522975029357</v>
+        <v>0.1515972282081392</v>
       </c>
       <c r="T62">
-        <v>2.010630275602593</v>
+        <v>2.062184898053942</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2491068760342809</v>
+        <v>0.2450231567550304</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2029609190011743</v>
+        <v>0.2048609190011743</v>
       </c>
       <c r="C63">
-        <v>-4.485233921138416</v>
+        <v>-4.890957739567023</v>
       </c>
       <c r="D63">
-        <v>6.64906607886158</v>
+        <v>6.569642260432973</v>
       </c>
       <c r="E63">
-        <v>12.9743</v>
+        <v>13.3006</v>
       </c>
       <c r="F63">
-        <v>19.9043</v>
+        <v>20.2306</v>
       </c>
       <c r="G63">
         <v>8.77</v>
@@ -6453,28 +6453,28 @@
         <v>1.15</v>
       </c>
       <c r="M63">
-        <v>4.693433939999999</v>
+        <v>4.770375479999999</v>
       </c>
       <c r="N63">
-        <v>-3.543433939999999</v>
+        <v>-3.620375479999999</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-3.543433939999999</v>
+        <v>-3.620375479999999</v>
       </c>
       <c r="Q63">
-        <v>-2.97343394</v>
+        <v>-3.05037548</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1515972282081392</v>
+        <v>0.1543813657925639</v>
       </c>
       <c r="T63">
-        <v>2.062184898053942</v>
+        <v>2.11645292168694</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2450231567550304</v>
+        <v>0.2410711703557558</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2048609190011743</v>
+        <v>0.2067609190011743</v>
       </c>
       <c r="C64">
-        <v>-4.890957739567023</v>
+        <v>-5.294806503405361</v>
       </c>
       <c r="D64">
-        <v>6.569642260432973</v>
+        <v>6.492093496594639</v>
       </c>
       <c r="E64">
-        <v>13.3006</v>
+        <v>13.6269</v>
       </c>
       <c r="F64">
-        <v>20.2306</v>
+        <v>20.5569</v>
       </c>
       <c r="G64">
         <v>8.77</v>
@@ -6535,28 +6535,28 @@
         <v>1.15</v>
       </c>
       <c r="M64">
-        <v>4.770375479999999</v>
+        <v>4.84731702</v>
       </c>
       <c r="N64">
-        <v>-3.620375479999999</v>
+        <v>-3.69731702</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-3.620375479999999</v>
+        <v>-3.69731702</v>
       </c>
       <c r="Q64">
-        <v>-3.05037548</v>
+        <v>-3.12731702</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1543813657925639</v>
+        <v>0.157315997300471</v>
       </c>
       <c r="T64">
-        <v>2.11645292168694</v>
+        <v>2.173654352002803</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2410711703557558</v>
+        <v>0.2372446438421723</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2067609190011743</v>
+        <v>0.2086609190011743</v>
       </c>
       <c r="C65">
-        <v>-5.294806503405361</v>
+        <v>-5.696845838042421</v>
       </c>
       <c r="D65">
-        <v>6.492093496594639</v>
+        <v>6.416354161957577</v>
       </c>
       <c r="E65">
-        <v>13.6269</v>
+        <v>13.9532</v>
       </c>
       <c r="F65">
-        <v>20.5569</v>
+        <v>20.8832</v>
       </c>
       <c r="G65">
         <v>8.77</v>
@@ -6617,28 +6617,28 @@
         <v>1.15</v>
       </c>
       <c r="M65">
-        <v>4.84731702</v>
+        <v>4.92425856</v>
       </c>
       <c r="N65">
-        <v>-3.69731702</v>
+        <v>-3.77425856</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-3.69731702</v>
+        <v>-3.77425856</v>
       </c>
       <c r="Q65">
-        <v>-3.12731702</v>
+        <v>-3.20425856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.157315997300471</v>
+        <v>0.1604136638921508</v>
       </c>
       <c r="T65">
-        <v>2.173654352002803</v>
+        <v>2.234033639558437</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2372446438421723</v>
+        <v>0.2335376962821384</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2086609190011743</v>
+        <v>0.2105609190011743</v>
       </c>
       <c r="C66">
-        <v>-5.696845838042421</v>
+        <v>-6.097138341735803</v>
       </c>
       <c r="D66">
-        <v>6.416354161957577</v>
+        <v>6.342361658264196</v>
       </c>
       <c r="E66">
-        <v>13.9532</v>
+        <v>14.2795</v>
       </c>
       <c r="F66">
-        <v>20.8832</v>
+        <v>21.2095</v>
       </c>
       <c r="G66">
         <v>8.77</v>
@@ -6699,28 +6699,28 @@
         <v>1.15</v>
       </c>
       <c r="M66">
-        <v>4.92425856</v>
+        <v>5.0012001</v>
       </c>
       <c r="N66">
-        <v>-3.77425856</v>
+        <v>-3.8512001</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-3.77425856</v>
+        <v>-3.8512001</v>
       </c>
       <c r="Q66">
-        <v>-3.20425856</v>
+        <v>-3.2812001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1604136638921508</v>
+        <v>0.1636883400033551</v>
       </c>
       <c r="T66">
-        <v>2.234033639558437</v>
+        <v>2.29786317211725</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2335376962821384</v>
+        <v>0.2299448086470285</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2105609190011743</v>
+        <v>0.2124609190011743</v>
       </c>
       <c r="C67">
-        <v>-6.097138341735803</v>
+        <v>-6.4957437581641</v>
       </c>
       <c r="D67">
-        <v>6.342361658264196</v>
+        <v>6.2700562418359</v>
       </c>
       <c r="E67">
-        <v>14.2795</v>
+        <v>14.6058</v>
       </c>
       <c r="F67">
-        <v>21.2095</v>
+        <v>21.5358</v>
       </c>
       <c r="G67">
         <v>8.77</v>
@@ -6781,28 +6781,28 @@
         <v>1.15</v>
       </c>
       <c r="M67">
-        <v>5.0012001</v>
+        <v>5.07814164</v>
       </c>
       <c r="N67">
-        <v>-3.8512001</v>
+        <v>-3.92814164</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-3.8512001</v>
+        <v>-3.92814164</v>
       </c>
       <c r="Q67">
-        <v>-3.2812001</v>
+        <v>-3.35814164</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1636883400033551</v>
+        <v>0.1671556441211008</v>
       </c>
       <c r="T67">
-        <v>2.29786317211725</v>
+        <v>2.365447383061874</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2299448086470285</v>
+        <v>0.2264607963948008</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2124609190011743</v>
+        <v>0.2143609190011743</v>
       </c>
       <c r="C68">
-        <v>-6.4957437581641</v>
+        <v>-6.892719137309397</v>
       </c>
       <c r="D68">
-        <v>6.2700562418359</v>
+        <v>6.199380862690601</v>
       </c>
       <c r="E68">
-        <v>14.6058</v>
+        <v>14.9321</v>
       </c>
       <c r="F68">
-        <v>21.5358</v>
+        <v>21.8621</v>
       </c>
       <c r="G68">
         <v>8.77</v>
@@ -6863,28 +6863,28 @@
         <v>1.15</v>
       </c>
       <c r="M68">
-        <v>5.07814164</v>
+        <v>5.15508318</v>
       </c>
       <c r="N68">
-        <v>-3.92814164</v>
+        <v>-4.00508318</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-3.92814164</v>
+        <v>-4.00508318</v>
       </c>
       <c r="Q68">
-        <v>-3.35814164</v>
+        <v>-3.435083179999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1671556441211008</v>
+        <v>0.1708330878823463</v>
       </c>
       <c r="T68">
-        <v>2.365447383061874</v>
+        <v>2.437127606791022</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2264607963948008</v>
+        <v>0.2230807845083114</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2143609190011743</v>
+        <v>0.2162609190011743</v>
       </c>
       <c r="C69">
-        <v>-6.892719137309397</v>
+        <v>-7.288118985580372</v>
       </c>
       <c r="D69">
-        <v>6.199380862690601</v>
+        <v>6.130281014419627</v>
       </c>
       <c r="E69">
-        <v>14.9321</v>
+        <v>15.2584</v>
       </c>
       <c r="F69">
-        <v>21.8621</v>
+        <v>22.1884</v>
       </c>
       <c r="G69">
         <v>8.77</v>
@@ -6945,28 +6945,28 @@
         <v>1.15</v>
       </c>
       <c r="M69">
-        <v>5.15508318</v>
+        <v>5.23202472</v>
       </c>
       <c r="N69">
-        <v>-4.00508318</v>
+        <v>-4.08202472</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-4.00508318</v>
+        <v>-4.08202472</v>
       </c>
       <c r="Q69">
-        <v>-3.435083179999999</v>
+        <v>-3.512024719999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1708330878823463</v>
+        <v>0.1747403718786696</v>
       </c>
       <c r="T69">
-        <v>2.437127606791022</v>
+        <v>2.513287844503242</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2230807845083114</v>
+        <v>0.2198001847361303</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2162609190011743</v>
+        <v>0.2181609190011743</v>
       </c>
       <c r="C70">
-        <v>-7.288118985580372</v>
+        <v>-7.681995406006152</v>
       </c>
       <c r="D70">
-        <v>6.130281014419627</v>
+        <v>6.062704593993845</v>
       </c>
       <c r="E70">
-        <v>15.2584</v>
+        <v>15.5847</v>
       </c>
       <c r="F70">
-        <v>22.1884</v>
+        <v>22.5147</v>
       </c>
       <c r="G70">
         <v>8.77</v>
@@ -7027,28 +7027,28 @@
         <v>1.15</v>
       </c>
       <c r="M70">
-        <v>5.23202472</v>
+        <v>5.30896626</v>
       </c>
       <c r="N70">
-        <v>-4.08202472</v>
+        <v>-4.15896626</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-4.08202472</v>
+        <v>-4.15896626</v>
       </c>
       <c r="Q70">
-        <v>-3.512024719999999</v>
+        <v>-3.588966259999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1747403718786696</v>
+        <v>0.1788997387134655</v>
       </c>
       <c r="T70">
-        <v>2.513287844503242</v>
+        <v>2.594361645938831</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2198001847361303</v>
+        <v>0.2166146748124183</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2181609190011743</v>
+        <v>0.2200609190011743</v>
       </c>
       <c r="C71">
-        <v>-7.681995406006152</v>
+        <v>-8.074398229258856</v>
       </c>
       <c r="D71">
-        <v>6.062704593993845</v>
+        <v>5.996601770741142</v>
       </c>
       <c r="E71">
-        <v>15.5847</v>
+        <v>15.911</v>
       </c>
       <c r="F71">
-        <v>22.5147</v>
+        <v>22.841</v>
       </c>
       <c r="G71">
         <v>8.77</v>
@@ -7109,28 +7109,28 @@
         <v>1.15</v>
       </c>
       <c r="M71">
-        <v>5.30896626</v>
+        <v>5.3859078</v>
       </c>
       <c r="N71">
-        <v>-4.15896626</v>
+        <v>-4.2359078</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-4.15896626</v>
+        <v>-4.2359078</v>
       </c>
       <c r="Q71">
-        <v>-3.588966259999999</v>
+        <v>-3.665907799999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1788997387134655</v>
+        <v>0.183336396670581</v>
       </c>
       <c r="T71">
-        <v>2.594361645938831</v>
+        <v>2.680840367470125</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2166146748124183</v>
+        <v>0.2135201794579551</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2200609190011743</v>
+        <v>0.2219609190011743</v>
       </c>
       <c r="C72">
-        <v>-8.074398229258856</v>
+        <v>-8.465375136197183</v>
       </c>
       <c r="D72">
-        <v>5.996601770741142</v>
+        <v>5.931924863802818</v>
       </c>
       <c r="E72">
-        <v>15.911</v>
+        <v>16.2373</v>
       </c>
       <c r="F72">
-        <v>22.841</v>
+        <v>23.1673</v>
       </c>
       <c r="G72">
         <v>8.77</v>
@@ -7191,28 +7191,28 @@
         <v>1.15</v>
       </c>
       <c r="M72">
-        <v>5.3859078</v>
+        <v>5.46284934</v>
       </c>
       <c r="N72">
-        <v>-4.2359078</v>
+        <v>-4.31284934</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-4.2359078</v>
+        <v>-4.31284934</v>
       </c>
       <c r="Q72">
-        <v>-3.665907799999999</v>
+        <v>-3.742849339999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.183336396670581</v>
+        <v>0.188079031038532</v>
       </c>
       <c r="T72">
-        <v>2.680840367470125</v>
+        <v>2.773283138762198</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2135201794579551</v>
+        <v>0.2105128529867163</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2219609190011743</v>
+        <v>0.2238609190011743</v>
       </c>
       <c r="C73">
-        <v>-8.46537513619718</v>
+        <v>-8.854971772564372</v>
       </c>
       <c r="D73">
-        <v>5.931924863802818</v>
+        <v>5.868628227435626</v>
       </c>
       <c r="E73">
-        <v>16.2373</v>
+        <v>16.5636</v>
       </c>
       <c r="F73">
-        <v>23.1673</v>
+        <v>23.4936</v>
       </c>
       <c r="G73">
         <v>8.77</v>
@@ -7273,28 +7273,28 @@
         <v>1.15</v>
       </c>
       <c r="M73">
-        <v>5.46284934</v>
+        <v>5.53979088</v>
       </c>
       <c r="N73">
-        <v>-4.31284934</v>
+        <v>-4.38979088</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-4.31284934</v>
+        <v>-4.38979088</v>
       </c>
       <c r="Q73">
-        <v>-3.742849339999999</v>
+        <v>-3.819790879999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.188079031038532</v>
+        <v>0.1931604250041939</v>
       </c>
       <c r="T73">
-        <v>2.773283138762197</v>
+        <v>2.872328965146561</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2105128529867163</v>
+        <v>0.2075890633619009</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2238609190011743</v>
+        <v>0.2257609190011743</v>
       </c>
       <c r="C74">
-        <v>-8.854971772564372</v>
+        <v>-9.243231856420437</v>
       </c>
       <c r="D74">
-        <v>5.868628227435626</v>
+        <v>5.806668143579561</v>
       </c>
       <c r="E74">
-        <v>16.5636</v>
+        <v>16.8899</v>
       </c>
       <c r="F74">
-        <v>23.4936</v>
+        <v>23.8199</v>
       </c>
       <c r="G74">
         <v>8.77</v>
@@ -7355,28 +7355,28 @@
         <v>1.15</v>
       </c>
       <c r="M74">
-        <v>5.53979088</v>
+        <v>5.61673242</v>
       </c>
       <c r="N74">
-        <v>-4.38979088</v>
+        <v>-4.46673242</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-4.38979088</v>
+        <v>-4.46673242</v>
       </c>
       <c r="Q74">
-        <v>-3.819790879999999</v>
+        <v>-3.896732419999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1931604250041939</v>
+        <v>0.1986182185228677</v>
       </c>
       <c r="T74">
-        <v>2.872328965146561</v>
+        <v>2.978711519411249</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2075890633619009</v>
+        <v>0.2047453775624227</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2257609190011743</v>
+        <v>0.2276609190011743</v>
       </c>
       <c r="C75">
-        <v>-9.243231856420437</v>
+        <v>-9.630197278839917</v>
       </c>
       <c r="D75">
-        <v>5.806668143579561</v>
+        <v>5.74600272116008</v>
       </c>
       <c r="E75">
-        <v>16.8899</v>
+        <v>17.2162</v>
       </c>
       <c r="F75">
-        <v>23.8199</v>
+        <v>24.1462</v>
       </c>
       <c r="G75">
         <v>8.77</v>
@@ -7437,28 +7437,28 @@
         <v>1.15</v>
       </c>
       <c r="M75">
-        <v>5.61673242</v>
+        <v>5.693673959999999</v>
       </c>
       <c r="N75">
-        <v>-4.46673242</v>
+        <v>-4.54367396</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-4.46673242</v>
+        <v>-4.54367396</v>
       </c>
       <c r="Q75">
-        <v>-3.896732419999999</v>
+        <v>-3.973673959999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1986182185228677</v>
+        <v>0.2044958423122088</v>
       </c>
       <c r="T75">
-        <v>2.978711519411249</v>
+        <v>3.093277347080912</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2047453775624227</v>
+        <v>0.2019785481359034</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2276609190011743</v>
+        <v>0.2295609190011743</v>
       </c>
       <c r="C76">
-        <v>-9.630197278839917</v>
+        <v>-10.01590819836266</v>
       </c>
       <c r="D76">
-        <v>5.74600272116008</v>
+        <v>5.686591801637336</v>
       </c>
       <c r="E76">
-        <v>17.2162</v>
+        <v>17.5425</v>
       </c>
       <c r="F76">
-        <v>24.1462</v>
+        <v>24.4725</v>
       </c>
       <c r="G76">
         <v>8.77</v>
@@ -7519,28 +7519,28 @@
         <v>1.15</v>
       </c>
       <c r="M76">
-        <v>5.693673959999999</v>
+        <v>5.770615499999999</v>
       </c>
       <c r="N76">
-        <v>-4.54367396</v>
+        <v>-4.6206155</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-4.54367396</v>
+        <v>-4.6206155</v>
       </c>
       <c r="Q76">
-        <v>-3.973673959999999</v>
+        <v>-4.050615499999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2044958423122088</v>
+        <v>0.2108436760046971</v>
       </c>
       <c r="T76">
-        <v>3.093277347080912</v>
+        <v>3.217008440964149</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2019785481359034</v>
+        <v>0.1992855008274247</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2295609190011743</v>
+        <v>0.2314609190011743</v>
       </c>
       <c r="C77">
-        <v>-10.01590819836266</v>
+        <v>-10.40040312964512</v>
       </c>
       <c r="D77">
-        <v>5.686591801637336</v>
+        <v>5.62839687035488</v>
       </c>
       <c r="E77">
-        <v>17.5425</v>
+        <v>17.8688</v>
       </c>
       <c r="F77">
-        <v>24.4725</v>
+        <v>24.7988</v>
       </c>
       <c r="G77">
         <v>8.77</v>
@@ -7601,28 +7601,28 @@
         <v>1.15</v>
       </c>
       <c r="M77">
-        <v>5.770615499999999</v>
+        <v>5.847557039999999</v>
       </c>
       <c r="N77">
-        <v>-4.6206155</v>
+        <v>-4.69755704</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-4.6206155</v>
+        <v>-4.69755704</v>
       </c>
       <c r="Q77">
-        <v>-4.050615499999999</v>
+        <v>-4.127557039999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2108436760046971</v>
+        <v>0.2177204958382262</v>
       </c>
       <c r="T77">
-        <v>3.217008440964149</v>
+        <v>3.351050459337655</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1992855008274247</v>
+        <v>0.1966633231849586</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2314609190011743</v>
+        <v>0.2333609190011743</v>
       </c>
       <c r="C78">
-        <v>-10.40040312964512</v>
+        <v>-10.78371902672337</v>
       </c>
       <c r="D78">
-        <v>5.62839687035488</v>
+        <v>5.571380973276623</v>
       </c>
       <c r="E78">
-        <v>17.8688</v>
+        <v>18.1951</v>
       </c>
       <c r="F78">
-        <v>24.7988</v>
+        <v>25.1251</v>
       </c>
       <c r="G78">
         <v>8.77</v>
@@ -7683,28 +7683,28 @@
         <v>1.15</v>
       </c>
       <c r="M78">
-        <v>5.847557039999999</v>
+        <v>5.924498579999999</v>
       </c>
       <c r="N78">
-        <v>-4.69755704</v>
+        <v>-4.774498579999999</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-4.69755704</v>
+        <v>-4.774498579999999</v>
       </c>
       <c r="Q78">
-        <v>-4.127557039999999</v>
+        <v>-4.204498579999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2177204958382262</v>
+        <v>0.2251953000051056</v>
       </c>
       <c r="T78">
-        <v>3.351050459337655</v>
+        <v>3.496748305395814</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1966633231849586</v>
+        <v>0.1941092540526864</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2333609190011743</v>
+        <v>0.2352609190011743</v>
       </c>
       <c r="C79">
-        <v>-10.78371902672337</v>
+        <v>-11.1658913612662</v>
       </c>
       <c r="D79">
-        <v>5.571380973276623</v>
+        <v>5.515508638733793</v>
       </c>
       <c r="E79">
-        <v>18.1951</v>
+        <v>18.5214</v>
       </c>
       <c r="F79">
-        <v>25.1251</v>
+        <v>25.4514</v>
       </c>
       <c r="G79">
         <v>8.77</v>
@@ -7765,28 +7765,28 @@
         <v>1.15</v>
       </c>
       <c r="M79">
-        <v>5.924498579999999</v>
+        <v>6.001440119999999</v>
       </c>
       <c r="N79">
-        <v>-4.774498579999999</v>
+        <v>-4.851440119999999</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-4.774498579999999</v>
+        <v>-4.851440119999999</v>
       </c>
       <c r="Q79">
-        <v>-4.204498579999999</v>
+        <v>-4.281440119999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2251953000051056</v>
+        <v>0.2333496318235195</v>
       </c>
       <c r="T79">
-        <v>3.496748305395814</v>
+        <v>3.655691410186533</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1941092540526864</v>
+        <v>0.1916206738725237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2352609190011743</v>
+        <v>0.2371609190011743</v>
       </c>
       <c r="C80">
-        <v>-11.1658913612662</v>
+        <v>-11.54695419616631</v>
       </c>
       <c r="D80">
-        <v>5.515508638733793</v>
+        <v>5.460745803833686</v>
       </c>
       <c r="E80">
-        <v>18.5214</v>
+        <v>18.8477</v>
       </c>
       <c r="F80">
-        <v>25.4514</v>
+        <v>25.7777</v>
       </c>
       <c r="G80">
         <v>8.77</v>
@@ -7847,28 +7847,28 @@
         <v>1.15</v>
       </c>
       <c r="M80">
-        <v>6.001440119999999</v>
+        <v>6.078381659999999</v>
       </c>
       <c r="N80">
-        <v>-4.851440119999999</v>
+        <v>-4.928381659999999</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-4.851440119999999</v>
+        <v>-4.928381659999999</v>
       </c>
       <c r="Q80">
-        <v>-4.281440119999999</v>
+        <v>-4.358381659999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2333496318235195</v>
+        <v>0.2422805666722585</v>
       </c>
       <c r="T80">
-        <v>3.655691410186533</v>
+        <v>3.82977195352875</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1916206738725237</v>
+        <v>0.1891950957222386</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2371609190011743</v>
+        <v>0.2390609190011743</v>
       </c>
       <c r="C81">
-        <v>-11.54695419616631</v>
+        <v>-11.92694025479062</v>
       </c>
       <c r="D81">
-        <v>5.460745803833686</v>
+        <v>5.40705974520938</v>
       </c>
       <c r="E81">
-        <v>18.8477</v>
+        <v>19.174</v>
       </c>
       <c r="F81">
-        <v>25.7777</v>
+        <v>26.104</v>
       </c>
       <c r="G81">
         <v>8.77</v>
@@ -7929,28 +7929,28 @@
         <v>1.15</v>
       </c>
       <c r="M81">
-        <v>6.078381659999999</v>
+        <v>6.1553232</v>
       </c>
       <c r="N81">
-        <v>-4.928381659999999</v>
+        <v>-5.005323199999999</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-4.928381659999999</v>
+        <v>-5.005323199999999</v>
       </c>
       <c r="Q81">
-        <v>-4.358381659999999</v>
+        <v>-4.435323199999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2422805666722585</v>
+        <v>0.2521045950058715</v>
       </c>
       <c r="T81">
-        <v>3.82977195352875</v>
+        <v>4.021260551205187</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1891950957222386</v>
+        <v>0.1868301570257107</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2390609190011743</v>
+        <v>0.2409609190011743</v>
       </c>
       <c r="C82">
-        <v>-11.92694025479062</v>
+        <v>-12.30588098618539</v>
       </c>
       <c r="D82">
-        <v>5.40705974520938</v>
+        <v>5.354419013814608</v>
       </c>
       <c r="E82">
-        <v>19.174</v>
+        <v>19.5003</v>
       </c>
       <c r="F82">
-        <v>26.104</v>
+        <v>26.4303</v>
       </c>
       <c r="G82">
         <v>8.77</v>
@@ -8011,28 +8011,28 @@
         <v>1.15</v>
       </c>
       <c r="M82">
-        <v>6.1553232</v>
+        <v>6.23226474</v>
       </c>
       <c r="N82">
-        <v>-5.005323199999999</v>
+        <v>-5.082264739999999</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-5.005323199999999</v>
+        <v>-5.082264739999999</v>
       </c>
       <c r="Q82">
-        <v>-4.435323199999999</v>
+        <v>-4.512264739999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2521045950058715</v>
+        <v>0.2629627315851278</v>
       </c>
       <c r="T82">
-        <v>4.021260551205187</v>
+        <v>4.232905843373882</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1868301570257107</v>
+        <v>0.1845236118772452</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2409609190011743</v>
+        <v>0.2428609190011743</v>
       </c>
       <c r="C83">
-        <v>-12.30588098618539</v>
+        <v>-12.68380662650927</v>
       </c>
       <c r="D83">
-        <v>5.354419013814608</v>
+        <v>5.302793373490728</v>
       </c>
       <c r="E83">
-        <v>19.5003</v>
+        <v>19.8266</v>
       </c>
       <c r="F83">
-        <v>26.4303</v>
+        <v>26.7566</v>
       </c>
       <c r="G83">
         <v>8.77</v>
@@ -8093,28 +8093,28 @@
         <v>1.15</v>
       </c>
       <c r="M83">
-        <v>6.23226474</v>
+        <v>6.30920628</v>
       </c>
       <c r="N83">
-        <v>-5.082264739999999</v>
+        <v>-5.159206279999999</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-5.082264739999999</v>
+        <v>-5.159206279999999</v>
       </c>
       <c r="Q83">
-        <v>-4.512264739999999</v>
+        <v>-4.589206279999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2629627315851278</v>
+        <v>0.2750273277843016</v>
       </c>
       <c r="T83">
-        <v>4.232905843373882</v>
+        <v>4.468067279116875</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1845236118772452</v>
+        <v>0.1822733239275227</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2428609190011743</v>
+        <v>0.2447609190011743</v>
       </c>
       <c r="C84">
-        <v>-12.68380662650927</v>
+        <v>-13.06074625694631</v>
       </c>
       <c r="D84">
-        <v>5.302793373490728</v>
+        <v>5.252153743053694</v>
       </c>
       <c r="E84">
-        <v>19.8266</v>
+        <v>20.1529</v>
       </c>
       <c r="F84">
-        <v>26.7566</v>
+        <v>27.0829</v>
       </c>
       <c r="G84">
         <v>8.77</v>
@@ -8175,28 +8175,28 @@
         <v>1.15</v>
       </c>
       <c r="M84">
-        <v>6.30920628</v>
+        <v>6.38614782</v>
       </c>
       <c r="N84">
-        <v>-5.159206279999999</v>
+        <v>-5.236147819999999</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-5.159206279999999</v>
+        <v>-5.236147819999999</v>
       </c>
       <c r="Q84">
-        <v>-4.589206279999999</v>
+        <v>-4.666147819999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2750273277843016</v>
+        <v>0.2885112882422017</v>
       </c>
       <c r="T84">
-        <v>4.468067279116875</v>
+        <v>4.73089476612375</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1822733239275227</v>
+        <v>0.1800772597838176</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2447609190011743</v>
+        <v>0.2466609190011743</v>
       </c>
       <c r="C85">
-        <v>-13.06074625694631</v>
+        <v>-13.43672785833211</v>
       </c>
       <c r="D85">
-        <v>5.252153743053694</v>
+        <v>5.202472141667891</v>
       </c>
       <c r="E85">
-        <v>20.1529</v>
+        <v>20.4792</v>
       </c>
       <c r="F85">
-        <v>27.0829</v>
+        <v>27.4092</v>
       </c>
       <c r="G85">
         <v>8.77</v>
@@ -8257,28 +8257,28 @@
         <v>1.15</v>
       </c>
       <c r="M85">
-        <v>6.38614782</v>
+        <v>6.46308936</v>
       </c>
       <c r="N85">
-        <v>-5.236147819999999</v>
+        <v>-5.313089359999999</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-5.236147819999999</v>
+        <v>-5.313089359999999</v>
       </c>
       <c r="Q85">
-        <v>-4.666147819999999</v>
+        <v>-4.743089359999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2885112882422017</v>
+        <v>0.3036807437573394</v>
       </c>
       <c r="T85">
-        <v>4.73089476612375</v>
+        <v>5.026575689006486</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1800772597838176</v>
+        <v>0.1779334828816292</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2466609190011743</v>
+        <v>0.2485609190011743</v>
       </c>
       <c r="C86">
-        <v>-13.4367278583321</v>
+        <v>-13.8117783627087</v>
       </c>
       <c r="D86">
-        <v>5.202472141667894</v>
+        <v>5.153721637291299</v>
       </c>
       <c r="E86">
-        <v>20.4792</v>
+        <v>20.80549999999999</v>
       </c>
       <c r="F86">
-        <v>27.40919999999999</v>
+        <v>27.73549999999999</v>
       </c>
       <c r="G86">
         <v>8.77</v>
@@ -8339,28 +8339,28 @@
         <v>1.15</v>
       </c>
       <c r="M86">
-        <v>6.463089359999999</v>
+        <v>6.540030899999999</v>
       </c>
       <c r="N86">
-        <v>-5.313089359999999</v>
+        <v>-5.390030899999999</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-5.313089359999999</v>
+        <v>-5.390030899999999</v>
       </c>
       <c r="Q86">
-        <v>-4.743089359999999</v>
+        <v>-4.820030899999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3036807437573392</v>
+        <v>0.3208727933411619</v>
       </c>
       <c r="T86">
-        <v>5.026575689006482</v>
+        <v>5.361680734940248</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1779334828816291</v>
+        <v>0.1758401477889041</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2485609190011743</v>
+        <v>0.2504609190011743</v>
       </c>
       <c r="C87">
-        <v>-13.8117783627087</v>
+        <v>-14.18592370200768</v>
       </c>
       <c r="D87">
-        <v>5.153721637291299</v>
+        <v>5.105876297992313</v>
       </c>
       <c r="E87">
-        <v>20.80549999999999</v>
+        <v>21.13179999999999</v>
       </c>
       <c r="F87">
-        <v>27.73549999999999</v>
+        <v>28.06179999999999</v>
       </c>
       <c r="G87">
         <v>8.77</v>
@@ -8421,28 +8421,28 @@
         <v>1.15</v>
       </c>
       <c r="M87">
-        <v>6.540030899999999</v>
+        <v>6.616972439999999</v>
       </c>
       <c r="N87">
-        <v>-5.390030899999999</v>
+        <v>-5.466972439999999</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-5.390030899999999</v>
+        <v>-5.466972439999999</v>
       </c>
       <c r="Q87">
-        <v>-4.820030899999999</v>
+        <v>-4.896972439999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3208727933411619</v>
+        <v>0.3405208500083877</v>
       </c>
       <c r="T87">
-        <v>5.361680734940248</v>
+        <v>5.744657930293123</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1758401477889041</v>
+        <v>0.1737954949076378</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2504609190011743</v>
+        <v>0.2523609190011743</v>
       </c>
       <c r="C88">
-        <v>-14.18592370200768</v>
+        <v>-14.55918885404659</v>
       </c>
       <c r="D88">
-        <v>5.105876297992313</v>
+        <v>5.05891114595341</v>
       </c>
       <c r="E88">
-        <v>21.13179999999999</v>
+        <v>21.45809999999999</v>
       </c>
       <c r="F88">
-        <v>28.06179999999999</v>
+        <v>28.38809999999999</v>
       </c>
       <c r="G88">
         <v>8.77</v>
@@ -8503,28 +8503,28 @@
         <v>1.15</v>
       </c>
       <c r="M88">
-        <v>6.616972439999999</v>
+        <v>6.693913979999999</v>
       </c>
       <c r="N88">
-        <v>-5.466972439999999</v>
+        <v>-5.543913979999999</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-5.466972439999999</v>
+        <v>-5.543913979999999</v>
       </c>
       <c r="Q88">
-        <v>-4.896972439999999</v>
+        <v>-4.973913979999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3405208500083877</v>
+        <v>0.3631916846244175</v>
       </c>
       <c r="T88">
-        <v>5.744657930293123</v>
+        <v>6.186554694161824</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1737954949076378</v>
+        <v>0.1717978455408834</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2523609190011743</v>
+        <v>0.2542609190011743</v>
       </c>
       <c r="C89">
-        <v>-14.55918885404659</v>
+        <v>-14.93159788600983</v>
       </c>
       <c r="D89">
-        <v>5.05891114595341</v>
+        <v>5.012802113990171</v>
       </c>
       <c r="E89">
-        <v>21.45809999999999</v>
+        <v>21.7844</v>
       </c>
       <c r="F89">
-        <v>28.38809999999999</v>
+        <v>28.7144</v>
       </c>
       <c r="G89">
         <v>8.77</v>
@@ -8585,28 +8585,28 @@
         <v>1.15</v>
       </c>
       <c r="M89">
-        <v>6.693913979999999</v>
+        <v>6.77085552</v>
       </c>
       <c r="N89">
-        <v>-5.543913979999999</v>
+        <v>-5.620855519999999</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-5.543913979999999</v>
+        <v>-5.620855519999999</v>
       </c>
       <c r="Q89">
-        <v>-4.973913979999999</v>
+        <v>-5.050855519999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3631916846244175</v>
+        <v>0.3896409916764524</v>
       </c>
       <c r="T89">
-        <v>6.186554694161824</v>
+        <v>6.702100918675311</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1717978455408834</v>
+        <v>0.1698455972961007</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2542609190011743</v>
+        <v>0.2561609190011743</v>
       </c>
       <c r="C90">
-        <v>-14.93159788600983</v>
+        <v>-15.30317399557336</v>
       </c>
       <c r="D90">
-        <v>5.012802113990171</v>
+        <v>4.967526004426642</v>
       </c>
       <c r="E90">
-        <v>21.7844</v>
+        <v>22.1107</v>
       </c>
       <c r="F90">
-        <v>28.7144</v>
+        <v>29.0407</v>
       </c>
       <c r="G90">
         <v>8.77</v>
@@ -8667,28 +8667,28 @@
         <v>1.15</v>
       </c>
       <c r="M90">
-        <v>6.77085552</v>
+        <v>6.84779706</v>
       </c>
       <c r="N90">
-        <v>-5.620855519999999</v>
+        <v>-5.697797059999999</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-5.620855519999999</v>
+        <v>-5.697797059999999</v>
       </c>
       <c r="Q90">
-        <v>-5.050855519999999</v>
+        <v>-5.127797059999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3896409916764524</v>
+        <v>0.4208992636470389</v>
       </c>
       <c r="T90">
-        <v>6.702100918675311</v>
+        <v>7.311382820373066</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1698455972961007</v>
+        <v>0.1679372197983917</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2561609190011743</v>
+        <v>0.2580609190011743</v>
       </c>
       <c r="C91">
-        <v>-15.30317399557336</v>
+        <v>-15.67393954982057</v>
       </c>
       <c r="D91">
-        <v>4.967526004426642</v>
+        <v>4.923060450179428</v>
       </c>
       <c r="E91">
-        <v>22.1107</v>
+        <v>22.437</v>
       </c>
       <c r="F91">
-        <v>29.0407</v>
+        <v>29.367</v>
       </c>
       <c r="G91">
         <v>8.77</v>
@@ -8749,28 +8749,28 @@
         <v>1.15</v>
       </c>
       <c r="M91">
-        <v>6.84779706</v>
+        <v>6.9247386</v>
       </c>
       <c r="N91">
-        <v>-5.697797059999999</v>
+        <v>-5.774738599999999</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-5.697797059999999</v>
+        <v>-5.774738599999999</v>
       </c>
       <c r="Q91">
-        <v>-5.127797059999999</v>
+        <v>-5.204738599999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4208992636470389</v>
+        <v>0.4584091900117429</v>
       </c>
       <c r="T91">
-        <v>7.311382820373066</v>
+        <v>8.042521102410374</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1679372197983917</v>
+        <v>0.1660712506895207</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2580609190011743</v>
+        <v>0.2599609190011743</v>
       </c>
       <c r="C92">
-        <v>-15.67393954982057</v>
+        <v>-16.04391612208672</v>
       </c>
       <c r="D92">
-        <v>4.923060450179428</v>
+        <v>4.879383877913273</v>
       </c>
       <c r="E92">
-        <v>22.437</v>
+        <v>22.7633</v>
       </c>
       <c r="F92">
-        <v>29.367</v>
+        <v>29.6933</v>
       </c>
       <c r="G92">
         <v>8.77</v>
@@ -8831,28 +8831,28 @@
         <v>1.15</v>
       </c>
       <c r="M92">
-        <v>6.9247386</v>
+        <v>7.001680139999999</v>
       </c>
       <c r="N92">
-        <v>-5.774738599999999</v>
+        <v>-5.851680139999999</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-5.774738599999999</v>
+        <v>-5.851680139999999</v>
       </c>
       <c r="Q92">
-        <v>-5.204738599999999</v>
+        <v>-5.281680139999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4584091900117429</v>
+        <v>0.5042546555686033</v>
       </c>
       <c r="T92">
-        <v>8.042521102410374</v>
+        <v>8.93613455823375</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1660712506895207</v>
+        <v>0.1642462918907347</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2599609190011743</v>
+        <v>0.2618609190011743</v>
       </c>
       <c r="C93">
-        <v>-16.04391612208672</v>
+        <v>-16.41312452685929</v>
       </c>
       <c r="D93">
-        <v>4.879383877913273</v>
+        <v>4.836475473140707</v>
       </c>
       <c r="E93">
-        <v>22.7633</v>
+        <v>23.0896</v>
       </c>
       <c r="F93">
-        <v>29.6933</v>
+        <v>30.0196</v>
       </c>
       <c r="G93">
         <v>8.77</v>
@@ -8913,28 +8913,28 @@
         <v>1.15</v>
       </c>
       <c r="M93">
-        <v>7.001680139999999</v>
+        <v>7.078621679999999</v>
       </c>
       <c r="N93">
-        <v>-5.851680139999999</v>
+        <v>-5.928621679999999</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-5.851680139999999</v>
+        <v>-5.928621679999999</v>
       </c>
       <c r="Q93">
-        <v>-5.281680139999999</v>
+        <v>-5.358621679999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5042546555686033</v>
+        <v>0.5615614875146788</v>
       </c>
       <c r="T93">
-        <v>8.93613455823375</v>
+        <v>10.05315137801297</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1642462918907347</v>
+        <v>0.1624610061093137</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2618609190011743</v>
+        <v>0.2637609190011743</v>
       </c>
       <c r="C94">
-        <v>-16.41312452685929</v>
+        <v>-16.78158485285295</v>
       </c>
       <c r="D94">
-        <v>4.836475473140707</v>
+        <v>4.794315147147047</v>
       </c>
       <c r="E94">
-        <v>23.0896</v>
+        <v>23.4159</v>
       </c>
       <c r="F94">
-        <v>30.0196</v>
+        <v>30.3459</v>
       </c>
       <c r="G94">
         <v>8.77</v>
@@ -8995,28 +8995,28 @@
         <v>1.15</v>
       </c>
       <c r="M94">
-        <v>7.078621679999999</v>
+        <v>7.155563219999999</v>
       </c>
       <c r="N94">
-        <v>-5.928621679999999</v>
+        <v>-6.005563219999999</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-5.928621679999999</v>
+        <v>-6.005563219999999</v>
       </c>
       <c r="Q94">
-        <v>-5.358621679999999</v>
+        <v>-5.435563219999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5615614875146788</v>
+        <v>0.6352417000167758</v>
       </c>
       <c r="T94">
-        <v>10.05315137801297</v>
+        <v>11.48931586058625</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1624610061093137</v>
+        <v>0.1607141135705039</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2637609190011743</v>
+        <v>0.2656609190011743</v>
       </c>
       <c r="C95">
-        <v>-16.78158485285295</v>
+        <v>-17.14931649436961</v>
       </c>
       <c r="D95">
-        <v>4.794315147147047</v>
+        <v>4.752883505630389</v>
       </c>
       <c r="E95">
-        <v>23.4159</v>
+        <v>23.7422</v>
       </c>
       <c r="F95">
-        <v>30.3459</v>
+        <v>30.6722</v>
       </c>
       <c r="G95">
         <v>8.77</v>
@@ -9077,28 +9077,28 @@
         <v>1.15</v>
       </c>
       <c r="M95">
-        <v>7.155563219999999</v>
+        <v>7.232504759999999</v>
       </c>
       <c r="N95">
-        <v>-6.005563219999999</v>
+        <v>-6.082504759999999</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-6.005563219999999</v>
+        <v>-6.082504759999999</v>
       </c>
       <c r="Q95">
-        <v>-5.435563219999999</v>
+        <v>-5.512504759999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6352417000167758</v>
+        <v>0.7334819833529053</v>
       </c>
       <c r="T95">
-        <v>11.48931586058625</v>
+        <v>13.40420183735063</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1607141135705039</v>
+        <v>0.1590043889580517</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2656609190011743</v>
+        <v>0.2675609190011743</v>
       </c>
       <c r="C96">
-        <v>-17.14931649436961</v>
+        <v>-17.51633818104629</v>
       </c>
       <c r="D96">
-        <v>4.752883505630389</v>
+        <v>4.712161818953712</v>
       </c>
       <c r="E96">
-        <v>23.7422</v>
+        <v>24.0685</v>
       </c>
       <c r="F96">
-        <v>30.6722</v>
+        <v>30.9985</v>
       </c>
       <c r="G96">
         <v>8.77</v>
@@ -9159,28 +9159,28 @@
         <v>1.15</v>
       </c>
       <c r="M96">
-        <v>7.232504759999999</v>
+        <v>7.309446299999999</v>
       </c>
       <c r="N96">
-        <v>-6.082504759999999</v>
+        <v>-6.159446299999999</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-6.082504759999999</v>
+        <v>-6.159446299999999</v>
       </c>
       <c r="Q96">
-        <v>-5.512504759999999</v>
+        <v>-5.589446299999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7334819833529053</v>
+        <v>0.8710183800234869</v>
       </c>
       <c r="T96">
-        <v>13.40420183735063</v>
+        <v>16.08504220482077</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1590043889580517</v>
+        <v>0.1573306585479669</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2675609190011743</v>
+        <v>0.2694609190011743</v>
       </c>
       <c r="C97">
-        <v>-17.51633818104629</v>
+        <v>-17.88266800608677</v>
       </c>
       <c r="D97">
-        <v>4.712161818953712</v>
+        <v>4.672131993913224</v>
       </c>
       <c r="E97">
-        <v>24.0685</v>
+        <v>24.3948</v>
       </c>
       <c r="F97">
-        <v>30.9985</v>
+        <v>31.3248</v>
       </c>
       <c r="G97">
         <v>8.77</v>
@@ -9241,28 +9241,28 @@
         <v>1.15</v>
       </c>
       <c r="M97">
-        <v>7.309446299999999</v>
+        <v>7.38638784</v>
       </c>
       <c r="N97">
-        <v>-6.159446299999999</v>
+        <v>-6.236387840000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-6.159446299999999</v>
+        <v>-6.236387840000001</v>
       </c>
       <c r="Q97">
-        <v>-5.589446299999999</v>
+        <v>-5.666387840000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8710183800234869</v>
+        <v>1.077322975029359</v>
       </c>
       <c r="T97">
-        <v>16.08504220482077</v>
+        <v>20.10630275602597</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1573306585479669</v>
+        <v>0.1556917975214255</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2694609190011743</v>
+        <v>0.2713609190011743</v>
       </c>
       <c r="C98">
-        <v>-17.88266800608677</v>
+        <v>-18.24832345306644</v>
       </c>
       <c r="D98">
-        <v>4.672131993913224</v>
+        <v>4.632776546933557</v>
       </c>
       <c r="E98">
-        <v>24.3948</v>
+        <v>24.7211</v>
       </c>
       <c r="F98">
-        <v>31.3248</v>
+        <v>31.6511</v>
       </c>
       <c r="G98">
         <v>8.77</v>
@@ -9323,28 +9323,28 @@
         <v>1.15</v>
       </c>
       <c r="M98">
-        <v>7.386387839999999</v>
+        <v>7.463329379999999</v>
       </c>
       <c r="N98">
-        <v>-6.236387839999999</v>
+        <v>-6.313329379999999</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-6.236387839999999</v>
+        <v>-6.313329379999999</v>
       </c>
       <c r="Q98">
-        <v>-5.666387839999999</v>
+        <v>-5.743329379999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.077322975029356</v>
+        <v>1.421163966705808</v>
       </c>
       <c r="T98">
-        <v>20.10630275602592</v>
+        <v>26.80840367470122</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1556917975214256</v>
+        <v>0.1540867274438852</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2713609190011743</v>
+        <v>0.2732609190011743</v>
       </c>
       <c r="C99">
-        <v>-18.24832345306644</v>
+        <v>-18.61332142139359</v>
       </c>
       <c r="D99">
-        <v>4.632776546933557</v>
+        <v>4.594078578606402</v>
       </c>
       <c r="E99">
-        <v>24.7211</v>
+        <v>25.0474</v>
       </c>
       <c r="F99">
-        <v>31.6511</v>
+        <v>31.9774</v>
       </c>
       <c r="G99">
         <v>8.77</v>
@@ -9405,28 +9405,28 @@
         <v>1.15</v>
       </c>
       <c r="M99">
-        <v>7.463329379999999</v>
+        <v>7.540270919999999</v>
       </c>
       <c r="N99">
-        <v>-6.313329379999999</v>
+        <v>-6.390270919999999</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-6.313329379999999</v>
+        <v>-6.390270919999999</v>
       </c>
       <c r="Q99">
-        <v>-5.743329379999999</v>
+        <v>-5.820270919999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.421163966705808</v>
+        <v>2.108845950058712</v>
       </c>
       <c r="T99">
-        <v>26.80840367470122</v>
+        <v>40.21260551205183</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1540867274438852</v>
+        <v>0.1525144138985394</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2732609190011743</v>
+        <v>0.2751609190011743</v>
       </c>
       <c r="C100">
-        <v>-18.61332142139359</v>
+        <v>-18.97767825050539</v>
       </c>
       <c r="D100">
-        <v>4.594078578606402</v>
+        <v>4.556021749494604</v>
       </c>
       <c r="E100">
-        <v>25.0474</v>
+        <v>25.37369999999999</v>
       </c>
       <c r="F100">
-        <v>31.9774</v>
+        <v>32.30369999999999</v>
       </c>
       <c r="G100">
         <v>8.77</v>
@@ -9487,28 +9487,28 @@
         <v>1.15</v>
       </c>
       <c r="M100">
-        <v>7.540270919999999</v>
+        <v>7.617212459999998</v>
       </c>
       <c r="N100">
-        <v>-6.390270919999999</v>
+        <v>-6.467212459999999</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-6.390270919999999</v>
+        <v>-6.467212459999999</v>
       </c>
       <c r="Q100">
-        <v>-5.820270919999999</v>
+        <v>-5.897212459999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.108845950058712</v>
+        <v>4.171891900117425</v>
       </c>
       <c r="T100">
-        <v>40.21260551205183</v>
+        <v>80.42521102410366</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1525144138985394</v>
+        <v>0.1509738642632005</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2751609190011743</v>
-      </c>
-      <c r="C101">
-        <v>-18.97767825050539</v>
-      </c>
-      <c r="D101">
-        <v>4.556021749494604</v>
-      </c>
-      <c r="E101">
-        <v>25.37369999999999</v>
-      </c>
-      <c r="F101">
-        <v>32.30369999999999</v>
-      </c>
-      <c r="G101">
-        <v>8.77</v>
-      </c>
-      <c r="H101">
-        <v>25.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.72</v>
-      </c>
-      <c r="K101">
-        <v>0.5700000000000001</v>
-      </c>
-      <c r="L101">
-        <v>1.15</v>
-      </c>
-      <c r="M101">
-        <v>7.617212459999998</v>
-      </c>
-      <c r="N101">
-        <v>-6.467212459999999</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-6.467212459999999</v>
-      </c>
-      <c r="Q101">
-        <v>-5.897212459999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.171891900117425</v>
-      </c>
-      <c r="T101">
-        <v>80.42521102410366</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1509738642632005</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
